--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,257 +1104,36 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 62755-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45092</v>
+        <v>46008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1953,46 +1953,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44895</v>
+        <v>45282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2058,46 +2058,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 51900-2021</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2115,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44462</v>
+        <v>44895</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2131,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2167,35 +2171,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2223,7 @@
         <v>44943</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2307,7 +2311,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 51900-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2325,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45057</v>
+        <v>44462</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,13 +2341,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2377,42 +2381,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62755-2025</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,10 +2430,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46008</v>
+        <v>44623</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2442,7 +2446,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2482,42 +2486,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2531,10 +2535,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45282</v>
+        <v>45057</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2547,13 +2551,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2583,50 +2587,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2692,39 +2692,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
         <v>44790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44487</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>44645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44712</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>44750</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>44532</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44746</v>
+        <v>45217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45350</v>
+        <v>45548</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45412</v>
+        <v>45887</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45217</v>
+        <v>46008</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4118,7 +4118,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4128,14 +4128,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45216</v>
+        <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 62757-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4201,14 +4201,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45345</v>
+        <v>46008</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4264,7 +4264,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44828</v>
+        <v>45805</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45476</v>
+        <v>45329</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45476</v>
+        <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4493,14 +4493,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45548</v>
+        <v>45812</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45145</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4639,14 +4639,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45887</v>
+        <v>46034</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4775,7 +4775,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45835</v>
+        <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
         <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4931,14 +4931,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45897</v>
+        <v>45055</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45565</v>
+        <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5023,13 +5023,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5072,7 +5067,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5082,14 +5077,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5102,7 +5097,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5145,7 +5140,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5162,7 +5157,7 @@
         <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5175,7 +5170,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5218,7 +5213,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5228,14 +5223,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5248,7 +5243,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5291,7 +5286,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5308,7 +5303,7 @@
         <v>45922</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5364,7 +5359,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5374,14 +5369,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45929</v>
+        <v>45726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5394,7 +5389,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.699999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5437,7 +5432,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5447,14 +5442,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45588</v>
+        <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5467,7 +5462,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5510,7 +5505,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 23592-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5524,10 +5519,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45931</v>
+        <v>44721</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5540,7 +5535,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5583,7 +5578,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45028</v>
+        <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5612,13 +5607,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5661,7 +5651,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5675,10 +5665,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44895</v>
+        <v>45931</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5691,7 +5681,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5734,7 +5724,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5751,7 +5741,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5764,7 +5754,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5807,7 +5797,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5821,10 +5811,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5837,7 +5827,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5880,7 +5870,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5894,10 +5884,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5910,7 +5900,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5953,7 +5943,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5967,10 +5957,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44805</v>
+        <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5983,7 +5973,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6026,7 +6016,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6040,10 +6030,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44895</v>
+        <v>44805</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6056,7 +6046,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6099,7 +6089,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6113,10 +6103,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44970</v>
+        <v>44943</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6129,7 +6119,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6172,7 +6162,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6186,10 +6176,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44943</v>
+        <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6202,7 +6192,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6245,7 +6235,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6259,10 +6249,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6275,7 +6265,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6318,7 +6308,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6335,7 +6325,7 @@
         <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6348,7 +6338,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6408,7 +6398,7 @@
         <v>44895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6464,7 +6454,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6474,14 +6464,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45386</v>
+        <v>44970</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6494,7 +6484,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6537,7 +6527,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6551,10 +6541,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45971</v>
+        <v>45588</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6567,7 +6557,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6610,7 +6600,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56672-2025</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6624,10 +6614,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45975</v>
+        <v>44809</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6640,7 +6630,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6683,7 +6673,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6697,10 +6687,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45982</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6713,7 +6703,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6756,7 +6746,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6766,14 +6756,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44704</v>
+        <v>44746</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6786,7 +6776,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6829,7 +6819,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6843,10 +6833,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46132</v>
+        <v>45350</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6859,7 +6849,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6902,7 +6892,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6912,14 +6902,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44809</v>
+        <v>44704</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6932,7 +6922,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6975,7 +6965,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6989,10 +6979,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46002</v>
+        <v>45971</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7005,7 +6995,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7048,7 +7038,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7062,10 +7052,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46002</v>
+        <v>46132</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7078,7 +7068,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7121,7 +7111,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 56672-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7135,10 +7125,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46008</v>
+        <v>45975</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7151,7 +7141,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7194,7 +7184,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7208,10 +7198,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7224,7 +7214,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7267,7 +7257,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62757-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7281,10 +7271,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7297,7 +7287,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7340,7 +7330,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7354,10 +7344,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45329</v>
+        <v>44712</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7370,7 +7360,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.9</v>
+        <v>23.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7413,7 +7403,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7427,10 +7417,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45392</v>
+        <v>45982</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7443,7 +7433,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7486,7 +7476,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7500,10 +7490,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45723</v>
+        <v>44828</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7516,7 +7506,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7559,7 +7549,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7573,10 +7563,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44712</v>
+        <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7589,7 +7579,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>23.3</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7632,7 +7622,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7646,10 +7636,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45587</v>
+        <v>45817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7662,7 +7652,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7705,7 +7695,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7719,10 +7709,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46034</v>
+        <v>45834</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7735,7 +7725,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7778,7 +7768,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7792,10 +7782,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45917</v>
+        <v>45589</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7808,7 +7798,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7851,7 +7841,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7865,10 +7855,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46036</v>
+        <v>46002</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7881,7 +7871,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7924,7 +7914,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7938,10 +7928,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45834</v>
+        <v>46002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7954,7 +7944,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7997,7 +7987,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8011,10 +8001,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45350</v>
+        <v>45723</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8027,7 +8017,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8070,7 +8060,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23592-2022</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8084,10 +8074,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44721</v>
+        <v>45216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8100,7 +8090,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8143,7 +8133,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8153,14 +8143,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45726</v>
+        <v>45817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8173,7 +8163,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8216,7 +8206,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8230,10 +8220,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45817</v>
+        <v>45587</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8246,7 +8236,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8289,7 +8279,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8299,14 +8289,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45589</v>
+        <v>45345</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8319,7 +8309,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8362,7 +8352,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8376,10 +8366,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45216</v>
+        <v>46245</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8392,7 +8382,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8435,7 +8425,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8449,10 +8439,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45817</v>
+        <v>45412</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8465,7 +8455,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8508,7 +8498,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8522,10 +8512,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45055</v>
+        <v>46206</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8538,7 +8528,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8581,7 +8571,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8595,10 +8585,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45216</v>
+        <v>44700</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8611,7 +8601,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8654,7 +8644,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8668,10 +8658,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44710</v>
+        <v>45170</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8684,7 +8674,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8727,7 +8717,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8741,10 +8731,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44746</v>
+        <v>46276</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8757,7 +8747,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.4</v>
+        <v>11.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8817,7 +8807,7 @@
         <v>45441</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8873,7 +8863,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8887,10 +8877,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46245</v>
+        <v>45392</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8903,7 +8893,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8946,7 +8936,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8956,14 +8946,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44700</v>
+        <v>44959</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8976,7 +8966,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9019,7 +9009,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9033,10 +9023,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44746</v>
+        <v>45565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9048,8 +9038,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9092,7 +9087,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9106,10 +9101,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46206</v>
+        <v>45476</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9122,7 +9117,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9165,7 +9160,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9175,14 +9170,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44959</v>
+        <v>45476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9195,7 +9190,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9238,7 +9233,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9252,10 +9247,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45170</v>
+        <v>45350</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9268,7 +9263,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9311,7 +9306,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9321,14 +9316,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45300</v>
+        <v>45028</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9340,8 +9335,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46276</v>
+        <v>45300</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>11.6</v>
+        <v>0.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9457,7 +9457,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45805</v>
+        <v>44746</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9530,7 +9530,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9540,14 +9540,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45812</v>
+        <v>44710</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>45539</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE117"/>
+  <dimension ref="A1:AE118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,144 +1108,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 62755-2025</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46008</v>
+        <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -1961,38 +1961,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 51900-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45282</v>
+        <v>44462</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2058,50 +2058,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2115,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2131,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2164,49 +2160,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2220,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44943</v>
+        <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2236,7 +2232,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2269,49 +2265,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51900-2021</t>
+          <t>A 62755-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2325,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44462</v>
+        <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2341,7 +2337,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2377,46 +2373,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2430,10 +2426,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44623</v>
+        <v>45057</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2446,13 +2442,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2482,46 +2478,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2535,10 +2531,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45057</v>
+        <v>45282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2551,13 +2547,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2587,46 +2583,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45092</v>
+        <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2692,39 +2692,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
         <v>44790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44487</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>44645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44712</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>44750</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 69614-2021</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44532</v>
+        <v>45345</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3680,7 +3680,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 69628-2021</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44532</v>
+        <v>45217</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 69614-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45217</v>
+        <v>44532</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 69628-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45548</v>
+        <v>44532</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45887</v>
+        <v>45216</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46008</v>
+        <v>45350</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4118,7 +4118,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4128,14 +4128,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45386</v>
+        <v>45412</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62757-2025</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46008</v>
+        <v>44746</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4264,7 +4264,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45805</v>
+        <v>44710</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45329</v>
+        <v>44828</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45887</v>
+        <v>44746</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>7.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4493,14 +4493,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45812</v>
+        <v>45588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4566,14 +4566,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45145</v>
+        <v>45887</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4629,7 +4629,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4639,14 +4639,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45897</v>
+        <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4712,14 +4712,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46034</v>
+        <v>45897</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4775,7 +4775,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46036</v>
+        <v>45476</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45835</v>
+        <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45055</v>
+        <v>45548</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45835</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5077,14 +5077,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5150,14 +5150,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
         <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5296,14 +5296,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45922</v>
+        <v>45145</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45726</v>
+        <v>44704</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23592-2022</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44721</v>
+        <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5578,7 +5578,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44746</v>
+        <v>46132</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45931</v>
+        <v>44895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5724,7 +5724,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5741,7 +5741,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5957,10 +5957,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44895</v>
+        <v>44805</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44805</v>
+        <v>44895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44943</v>
+        <v>44970</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6162,7 +6162,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44517</v>
+        <v>44943</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6325,7 +6325,7 @@
         <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
         <v>44895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44970</v>
+        <v>45723</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45588</v>
+        <v>44712</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>23.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44809</v>
+        <v>45917</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6673,7 +6673,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>45565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6702,8 +6702,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6746,7 +6751,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6760,10 +6765,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44746</v>
+        <v>45834</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6776,7 +6781,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6819,7 +6824,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6833,10 +6838,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45350</v>
+        <v>45971</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6849,7 +6854,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6892,7 +6897,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6902,14 +6907,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44704</v>
+        <v>45441</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6922,7 +6927,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6965,7 +6970,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 56672-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6979,10 +6984,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6995,7 +7000,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7038,7 +7043,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7052,10 +7057,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46132</v>
+        <v>45817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7068,7 +7073,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7111,7 +7116,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56672-2025</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7125,10 +7130,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45975</v>
+        <v>45028</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7140,8 +7145,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7184,7 +7194,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7198,10 +7208,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45216</v>
+        <v>45589</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7214,7 +7224,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7257,7 +7267,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7271,10 +7281,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45216</v>
+        <v>45982</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7287,7 +7297,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7330,7 +7340,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7340,14 +7350,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44712</v>
+        <v>45386</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7360,7 +7370,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>23.3</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7403,7 +7413,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7417,10 +7427,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45982</v>
+        <v>44700</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7433,7 +7443,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7476,7 +7486,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7490,10 +7500,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44828</v>
+        <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7506,7 +7516,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7549,7 +7559,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7563,10 +7573,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45917</v>
+        <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7579,7 +7589,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7622,7 +7632,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7636,10 +7646,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45817</v>
+        <v>46008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7652,7 +7662,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7695,7 +7705,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7709,10 +7719,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7768,7 +7778,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 62757-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7782,10 +7792,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45589</v>
+        <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7798,7 +7808,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7841,7 +7851,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7855,10 +7865,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46002</v>
+        <v>45216</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7871,7 +7881,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7914,7 +7924,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7928,10 +7938,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46002</v>
+        <v>44746</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7944,7 +7954,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7987,7 +7997,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8001,10 +8011,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45723</v>
+        <v>45329</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8017,7 +8027,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8060,7 +8070,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8074,10 +8084,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45216</v>
+        <v>45817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8090,7 +8100,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8133,7 +8143,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8147,10 +8157,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45817</v>
+        <v>46034</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8163,7 +8173,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8206,7 +8216,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8220,10 +8230,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45587</v>
+        <v>46036</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8236,7 +8246,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8279,7 +8289,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8289,14 +8299,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45345</v>
+        <v>44809</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8309,7 +8319,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8352,7 +8362,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 23592-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8366,10 +8376,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46245</v>
+        <v>44721</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8382,7 +8392,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8425,7 +8435,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8435,14 +8445,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45412</v>
+        <v>45726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8455,7 +8465,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8498,7 +8508,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8512,10 +8522,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46206</v>
+        <v>45392</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8528,7 +8538,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8571,7 +8581,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8585,10 +8595,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44700</v>
+        <v>45587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8601,7 +8611,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8644,7 +8654,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8658,10 +8668,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45170</v>
+        <v>45350</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8674,7 +8684,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8717,7 +8727,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8727,14 +8737,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46276</v>
+        <v>44959</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8747,7 +8757,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>11.6</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8790,7 +8800,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8800,14 +8810,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45441</v>
+        <v>46245</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8820,7 +8830,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8863,7 +8873,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8877,10 +8887,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45392</v>
+        <v>46206</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8893,7 +8903,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8936,7 +8946,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8946,14 +8956,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44959</v>
+        <v>45170</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8966,7 +8976,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9009,7 +9019,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9023,10 +9033,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45565</v>
+        <v>45055</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9038,13 +9048,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9087,7 +9092,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9101,10 +9106,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45476</v>
+        <v>45216</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9117,7 +9122,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9160,7 +9165,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9170,14 +9175,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45476</v>
+        <v>45300</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9190,7 +9195,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9233,7 +9238,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9247,10 +9252,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45350</v>
+        <v>46276</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9263,7 +9268,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>11.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9306,7 +9311,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 37911-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9316,14 +9321,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45028</v>
+        <v>46279</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9335,13 +9340,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45300</v>
+        <v>45805</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9457,7 +9457,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9467,14 +9467,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44746</v>
+        <v>45812</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9530,7 +9530,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44710</v>
+        <v>45835</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9603,148 +9603,221 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
+          <t>A 32093-2025</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>S 3456-2024</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D116" s="1" t="n">
+      <c r="D117" s="1" t="n">
         <v>45539</v>
       </c>
-      <c r="E116" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I116" t="n">
+      <c r="E117" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
         <v>1.2</v>
       </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>S 3064-2024</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D117" s="1" t="n">
+      <c r="D118" s="1" t="n">
         <v>45517</v>
       </c>
-      <c r="E117" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I117" t="n">
+      <c r="E118" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
         <v>0.2</v>
       </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" s="2" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE118"/>
+  <dimension ref="A1:AE117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,257 +1104,36 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 51900-2021</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44462</v>
+        <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2055,49 +2055,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 51900-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44943</v>
+        <v>44462</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2160,49 +2160,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45092</v>
+        <v>45282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2268,46 +2268,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62755-2025</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2325,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46008</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,7 +2341,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2377,42 +2381,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 62755-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,10 +2430,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45057</v>
+        <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2442,13 +2446,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2478,46 +2482,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2531,10 +2535,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45282</v>
+        <v>45057</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2547,13 +2551,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2583,50 +2587,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2692,39 +2692,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
         <v>44790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44487</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>44645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44712</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>44750</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 69614-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45345</v>
+        <v>44532</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3680,7 +3680,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 69628-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45217</v>
+        <v>44532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 69614-2021</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44532</v>
+        <v>45217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 69628-2021</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44532</v>
+        <v>45548</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45216</v>
+        <v>45386</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3982,14 +3982,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45216</v>
+        <v>45145</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45350</v>
+        <v>45887</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4118,7 +4118,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45412</v>
+        <v>45805</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44746</v>
+        <v>45887</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4264,7 +4264,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4274,14 +4274,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44710</v>
+        <v>45812</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44828</v>
+        <v>45055</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4420,14 +4420,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44746</v>
+        <v>45897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45588</v>
+        <v>46034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45887</v>
+        <v>44746</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>7.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4629,7 +4629,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45887</v>
+        <v>45835</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4712,14 +4712,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45897</v>
+        <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4775,7 +4775,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45476</v>
+        <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4858,14 +4858,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45476</v>
+        <v>45919</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45548</v>
+        <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5011,7 +5011,7 @@
         <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45919</v>
+        <v>45929</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5213,7 +5213,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45922</v>
+        <v>45931</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5286,7 +5286,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5296,14 +5296,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45145</v>
+        <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5359,7 +5359,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44704</v>
+        <v>44895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5442,14 +5442,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45929</v>
+        <v>44895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.699999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45931</v>
+        <v>44895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46132</v>
+        <v>44805</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5724,7 +5724,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5741,7 +5741,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5814,7 +5814,7 @@
         <v>44517</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5957,10 +5957,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44805</v>
+        <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44895</v>
+        <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>44970</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44943</v>
+        <v>45588</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44895</v>
+        <v>45216</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44895</v>
+        <v>44746</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44895</v>
+        <v>45350</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6464,14 +6464,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 23592-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44712</v>
+        <v>44721</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>23.3</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45917</v>
+        <v>45971</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6673,7 +6673,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45565</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6702,13 +6702,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6751,7 +6746,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6765,10 +6760,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45834</v>
+        <v>45216</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6781,7 +6776,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6824,7 +6819,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 56672-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6838,10 +6833,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6854,7 +6849,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6897,7 +6892,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6907,14 +6902,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45441</v>
+        <v>45982</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6927,7 +6922,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6970,7 +6965,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56672-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6984,10 +6979,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45975</v>
+        <v>44828</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7000,7 +6995,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7043,7 +7038,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7057,10 +7052,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45817</v>
+        <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7116,7 +7111,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7130,10 +7125,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45028</v>
+        <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7145,13 +7140,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7194,7 +7184,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7208,10 +7198,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45589</v>
+        <v>46008</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7224,7 +7214,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7267,7 +7257,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7281,10 +7271,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45982</v>
+        <v>46008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7297,7 +7287,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7340,7 +7330,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 62757-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7350,14 +7340,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45386</v>
+        <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7370,7 +7360,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7413,7 +7403,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7427,10 +7417,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44700</v>
+        <v>45329</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7443,7 +7433,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7486,7 +7476,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7500,10 +7490,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46002</v>
+        <v>45587</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7516,7 +7506,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7559,7 +7549,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7569,14 +7559,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46002</v>
+        <v>44704</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7589,7 +7579,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7632,7 +7622,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7642,14 +7632,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46008</v>
+        <v>45345</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7662,7 +7652,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7705,7 +7695,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7719,10 +7709,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46008</v>
+        <v>46132</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7735,7 +7725,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7778,7 +7768,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62757-2025</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7792,10 +7782,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46008</v>
+        <v>45412</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7808,7 +7798,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7851,7 +7841,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7865,10 +7855,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45216</v>
+        <v>44712</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7881,7 +7871,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>23.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7924,7 +7914,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7938,10 +7928,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44746</v>
+        <v>45917</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7954,7 +7944,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7997,7 +7987,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8011,10 +8001,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45329</v>
+        <v>45817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8027,7 +8017,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8070,7 +8060,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8084,10 +8074,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45817</v>
+        <v>45834</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8100,7 +8090,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8143,7 +8133,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8157,10 +8147,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46034</v>
+        <v>45589</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8173,7 +8163,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8216,7 +8206,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8230,10 +8220,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46036</v>
+        <v>45723</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8246,7 +8236,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8289,7 +8279,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8303,10 +8293,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44809</v>
+        <v>44700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8319,7 +8309,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8362,7 +8352,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 23592-2022</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8376,10 +8366,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44721</v>
+        <v>45170</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8392,7 +8382,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8435,7 +8425,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8445,14 +8435,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45726</v>
+        <v>45216</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8465,7 +8455,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8508,7 +8498,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8518,14 +8508,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45392</v>
+        <v>45441</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8581,7 +8571,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8595,10 +8585,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45587</v>
+        <v>45392</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8611,7 +8601,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8654,7 +8644,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8668,10 +8658,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45350</v>
+        <v>45817</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8684,7 +8674,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8744,7 +8734,7 @@
         <v>44959</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8800,7 +8790,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8814,10 +8804,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46245</v>
+        <v>45565</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8829,8 +8819,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8873,7 +8868,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8887,10 +8882,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46206</v>
+        <v>45476</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8903,7 +8898,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8946,7 +8941,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8960,10 +8955,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45170</v>
+        <v>45476</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8976,7 +8971,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9019,7 +9014,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9033,10 +9028,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45055</v>
+        <v>45350</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9049,7 +9044,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9092,7 +9087,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9106,10 +9101,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45216</v>
+        <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9122,7 +9117,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9165,7 +9160,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9175,14 +9170,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45300</v>
+        <v>46206</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9195,7 +9190,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9238,7 +9233,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9252,10 +9247,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46276</v>
+        <v>45028</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9267,8 +9262,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>11.6</v>
+        <v>4.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9311,7 +9311,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37911-2026</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46279</v>
+        <v>45300</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45805</v>
+        <v>44746</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9457,7 +9457,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9467,14 +9467,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45812</v>
+        <v>44710</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9530,7 +9530,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45835</v>
+        <v>46276</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>11.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9603,24 +9603,24 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>S 3456-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45835</v>
+        <v>45539</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9673,10 +9673,10 @@
       </c>
       <c r="V116" s="2" t="inlineStr"/>
     </row>
-    <row r="117" ht="15" customHeight="1">
+    <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 3456-2024</t>
+          <t>S 3064-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9690,10 +9690,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45539</v>
+        <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9745,79 +9745,6 @@
         <v>0</v>
       </c>
       <c r="V117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>S 3064-2024</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="n">
-        <v>45517</v>
-      </c>
-      <c r="E118" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I118" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,144 +1108,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2447-2023</t>
+          <t>A 58073-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44943</v>
+        <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1526,146 +1526,146 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 58073-2025 artfynd.xlsx", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 58073-2025 karta.png", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 58073-2025 georefererad karta.tif", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 58073-2025 FSC-klagomål.docx", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 58073-2025 FSC-klagomål mail.docx", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 58073-2025 tillsynsbegäran.docx", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 58073-2025 tillsynsbegäran mail.docx", "A 58073-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 2447-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Dolkstekelsglasvinge
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2447-2023 artfynd.xlsx", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2447-2023 karta.png", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2447-2023 georefererad karta.tif", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2447-2023 FSC-klagomål.docx", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2447-2023 FSC-klagomål mail.docx", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2447-2023 tillsynsbegäran.docx", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2447-2023 tillsynsbegäran mail.docx", "A 2447-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 58073-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45982</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Kambräken</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 58073-2025 artfynd.xlsx", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 58073-2025 karta.png", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 58073-2025 georefererad karta.tif", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 58073-2025 FSC-klagomål.docx", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 58073-2025 FSC-klagomål mail.docx", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 58073-2025 tillsynsbegäran.docx", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 58073-2025 tillsynsbegäran mail.docx", "A 58073-2025")</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44895</v>
+        <v>45092</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1957,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44943</v>
+        <v>45057</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2055,49 +2055,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 51900-2021</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44462</v>
+        <v>44895</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2167,42 +2167,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 51900-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45282</v>
+        <v>44462</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2268,50 +2268,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2325,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2341,13 +2337,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2374,49 +2370,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62755-2025</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2430,10 +2426,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46008</v>
+        <v>44623</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2446,7 +2442,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2486,42 +2482,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 62755-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2535,10 +2531,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45057</v>
+        <v>46008</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2551,13 +2547,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2587,46 +2583,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2640,10 +2636,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45092</v>
+        <v>45282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2656,13 +2652,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2692,39 +2688,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
         <v>44790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44487</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>44645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44712</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>44750</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>44532</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45217</v>
+        <v>44746</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45548</v>
+        <v>45350</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45386</v>
+        <v>45412</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45145</v>
+        <v>45345</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45887</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4118,7 +4118,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45805</v>
+        <v>45216</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45887</v>
+        <v>44828</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4264,7 +4264,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4274,14 +4274,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45812</v>
+        <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45055</v>
+        <v>45476</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4420,14 +4420,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45897</v>
+        <v>45476</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46034</v>
+        <v>45548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4566,14 +4566,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44746</v>
+        <v>45145</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.4</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4629,7 +4629,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45835</v>
+        <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46036</v>
+        <v>45835</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4858,14 +4858,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45919</v>
+        <v>45887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45922</v>
+        <v>45565</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4950,8 +4950,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4994,7 +4999,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5008,10 +5013,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45028</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5023,8 +5028,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5067,7 +5077,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5077,14 +5087,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>45386</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5107,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5140,7 +5150,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5150,14 +5160,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45929</v>
+        <v>44704</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5180,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5213,7 +5223,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5223,14 +5233,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45931</v>
+        <v>45897</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5286,7 +5296,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5300,10 +5310,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44517</v>
+        <v>46132</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5316,7 +5326,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5359,7 +5369,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5373,10 +5383,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44895</v>
+        <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5389,7 +5399,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5432,7 +5442,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5446,10 +5456,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44895</v>
+        <v>45922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5462,7 +5472,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5505,7 +5515,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5519,10 +5529,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44895</v>
+        <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5535,7 +5545,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5578,7 +5588,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5588,14 +5598,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44805</v>
+        <v>45919</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5608,7 +5618,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5651,7 +5661,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5665,10 +5675,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44943</v>
+        <v>45723</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5681,7 +5691,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5724,7 +5734,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5738,10 +5748,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44517</v>
+        <v>45922</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5754,7 +5764,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5797,7 +5807,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5811,10 +5821,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44517</v>
+        <v>44712</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5827,7 +5837,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>23.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5870,7 +5880,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5884,10 +5894,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44895</v>
+        <v>45917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5900,7 +5910,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5943,7 +5953,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5957,10 +5967,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44895</v>
+        <v>45834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5973,7 +5983,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6016,7 +6026,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6030,10 +6040,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44809</v>
+        <v>45817</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6046,7 +6056,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6089,7 +6099,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6103,10 +6113,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44970</v>
+        <v>45589</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6119,7 +6129,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6162,7 +6172,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6176,10 +6186,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45588</v>
+        <v>44809</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6192,7 +6202,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6235,7 +6245,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6245,14 +6255,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45216</v>
+        <v>45929</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6265,7 +6275,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6308,7 +6318,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6322,10 +6332,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44746</v>
+        <v>45931</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6338,7 +6348,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6381,7 +6391,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6395,10 +6405,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45350</v>
+        <v>44895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6411,7 +6421,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6454,7 +6464,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6464,14 +6474,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45726</v>
+        <v>44517</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6484,7 +6494,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6527,7 +6537,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23592-2022</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6541,10 +6551,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44721</v>
+        <v>44517</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6557,7 +6567,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6600,7 +6610,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6614,10 +6624,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45971</v>
+        <v>44517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6630,7 +6640,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6673,7 +6683,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6687,10 +6697,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>44805</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6703,7 +6713,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6746,7 +6756,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6760,10 +6770,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45216</v>
+        <v>44895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6776,7 +6786,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6819,7 +6829,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56672-2025</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6833,10 +6843,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45975</v>
+        <v>44970</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6849,7 +6859,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6892,7 +6902,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6906,10 +6916,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45982</v>
+        <v>44943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6922,7 +6932,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6965,7 +6975,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6979,10 +6989,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44828</v>
+        <v>44895</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6995,7 +7005,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7038,7 +7048,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7052,10 +7062,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46002</v>
+        <v>44895</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7068,7 +7078,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7111,7 +7121,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7125,10 +7135,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46002</v>
+        <v>44895</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7141,7 +7151,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7184,7 +7194,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7198,10 +7208,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7214,7 +7224,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7257,7 +7267,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7271,10 +7281,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46008</v>
+        <v>45392</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7287,7 +7297,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7330,7 +7340,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62757-2025</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7344,10 +7354,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46008</v>
+        <v>45817</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7360,7 +7370,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7403,7 +7413,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7417,10 +7427,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45329</v>
+        <v>45587</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7433,7 +7443,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7476,7 +7486,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7490,10 +7500,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45587</v>
+        <v>45350</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7549,7 +7559,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7559,14 +7569,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44704</v>
+        <v>45971</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7579,7 +7589,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7622,7 +7632,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 56672-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7632,14 +7642,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45345</v>
+        <v>45975</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7652,7 +7662,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7695,7 +7705,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7709,10 +7719,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46132</v>
+        <v>45055</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7725,7 +7735,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7768,7 +7778,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7782,10 +7792,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45412</v>
+        <v>46245</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7798,7 +7808,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7841,7 +7851,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7855,10 +7865,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44712</v>
+        <v>45982</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7871,7 +7881,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>23.3</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7914,7 +7924,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7928,10 +7938,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45917</v>
+        <v>45216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7944,7 +7954,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7987,7 +7997,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8001,10 +8011,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45817</v>
+        <v>46206</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8017,7 +8027,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8060,7 +8070,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8074,10 +8084,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45834</v>
+        <v>44710</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8090,7 +8100,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8133,7 +8143,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8147,10 +8157,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45589</v>
+        <v>44746</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8163,7 +8173,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8206,7 +8216,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8220,10 +8230,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45723</v>
+        <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8236,7 +8246,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8279,7 +8289,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8293,10 +8303,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44700</v>
+        <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8309,7 +8319,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8352,7 +8362,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8366,10 +8376,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45170</v>
+        <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8382,7 +8392,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8425,7 +8435,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8439,10 +8449,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45216</v>
+        <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8455,7 +8465,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8498,7 +8508,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 62757-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8508,14 +8518,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45441</v>
+        <v>46008</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8528,7 +8538,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8571,7 +8581,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8585,10 +8595,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45392</v>
+        <v>45329</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8601,7 +8611,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8644,7 +8654,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8658,10 +8668,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45817</v>
+        <v>46276</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8674,7 +8684,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>11.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8717,7 +8727,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8731,10 +8741,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44959</v>
+        <v>45441</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8747,7 +8757,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8790,7 +8800,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8804,10 +8814,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45565</v>
+        <v>44700</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8819,13 +8829,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8868,7 +8873,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8882,10 +8887,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45476</v>
+        <v>44746</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8898,7 +8903,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8941,7 +8946,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8955,10 +8960,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45476</v>
+        <v>46034</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8971,7 +8976,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9014,7 +9019,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9028,10 +9033,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45350</v>
+        <v>46036</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9044,7 +9049,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9087,7 +9092,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9097,14 +9102,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46245</v>
+        <v>44959</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9117,7 +9122,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9160,7 +9165,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 23592-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9174,10 +9179,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46206</v>
+        <v>44721</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9190,7 +9195,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9233,7 +9238,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9243,14 +9248,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45028</v>
+        <v>45726</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9262,13 +9267,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9311,7 +9311,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45300</v>
+        <v>45170</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44746</v>
+        <v>45300</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9457,7 +9457,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44710</v>
+        <v>45805</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9530,7 +9530,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9540,14 +9540,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46276</v>
+        <v>45812</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>11.6</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>45539</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,264 +1104,43 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 55111-2025</t>
+          <t>A 22268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45968</v>
+        <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>16.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1206,148 +1206,148 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Havstulpanlav
+Stubbspretmossa
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 55111-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stor revmossa
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 22268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44712</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Havstulpanlav
-Stubbspretmossa
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>44943</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45092</v>
+        <v>44623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1953,46 +1953,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45057</v>
+        <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2062,42 +2062,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2160,42 +2160,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>44462</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44943</v>
+        <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2370,49 +2370,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2478,39 +2478,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
         <v>46008</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44487</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>44645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44712</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>44750</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>44532</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44746</v>
+        <v>45217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45350</v>
+        <v>45548</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45412</v>
+        <v>45386</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45345</v>
+        <v>45145</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>45055</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4118,7 +4118,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45216</v>
+        <v>44746</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44828</v>
+        <v>44809</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4264,7 +4264,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45217</v>
+        <v>45216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45476</v>
+        <v>45350</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45476</v>
+        <v>44746</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45548</v>
+        <v>45216</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4566,14 +4566,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45145</v>
+        <v>45216</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
         <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45835</v>
+        <v>44828</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4775,7 +4775,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45835</v>
+        <v>45917</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45887</v>
+        <v>45817</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45565</v>
+        <v>45834</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4950,13 +4950,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4999,7 +4994,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5013,10 +5008,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45028</v>
+        <v>45589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5028,13 +5023,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5077,7 +5067,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5091,10 +5081,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45386</v>
+        <v>45897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5107,7 +5097,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5150,7 +5140,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5160,14 +5150,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44704</v>
+        <v>45887</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5180,7 +5170,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5223,7 +5213,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5233,14 +5223,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45897</v>
+        <v>45723</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5253,7 +5243,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5296,7 +5286,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5306,14 +5296,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46132</v>
+        <v>45919</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5326,7 +5316,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5369,7 +5359,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5383,10 +5373,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45588</v>
+        <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5399,7 +5389,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5442,7 +5432,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5459,7 +5449,7 @@
         <v>45922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5472,7 +5462,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5532,7 +5522,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5588,7 +5578,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5602,10 +5592,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45919</v>
+        <v>45929</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5618,7 +5608,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5661,7 +5651,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5675,10 +5665,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45723</v>
+        <v>45931</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5691,7 +5681,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5734,7 +5724,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5748,10 +5738,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45922</v>
+        <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5764,7 +5754,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5807,7 +5797,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5821,10 +5811,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44712</v>
+        <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5837,7 +5827,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>23.3</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5880,7 +5870,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5894,10 +5884,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45917</v>
+        <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5910,7 +5900,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5953,7 +5943,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5967,10 +5957,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45834</v>
+        <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5983,7 +5973,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6026,7 +6016,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6040,10 +6030,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45817</v>
+        <v>44805</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6056,7 +6046,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6099,7 +6089,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6113,10 +6103,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45589</v>
+        <v>44943</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6129,7 +6119,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6172,7 +6162,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6186,10 +6176,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44809</v>
+        <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6202,7 +6192,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6245,7 +6235,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6255,14 +6245,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45929</v>
+        <v>44517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6275,7 +6265,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6318,7 +6308,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6332,10 +6322,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45931</v>
+        <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6348,7 +6338,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6391,7 +6381,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6408,7 +6398,7 @@
         <v>44895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6421,7 +6411,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6464,7 +6454,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6478,10 +6468,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44517</v>
+        <v>44970</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6494,7 +6484,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6537,7 +6527,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6551,10 +6541,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44517</v>
+        <v>45587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6567,7 +6557,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6610,7 +6600,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6620,14 +6610,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44517</v>
+        <v>45345</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6640,7 +6630,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6683,7 +6673,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6697,10 +6687,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44805</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6713,7 +6703,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6756,7 +6746,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6770,10 +6760,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44895</v>
+        <v>45412</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6786,7 +6776,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6829,7 +6819,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6843,10 +6833,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44970</v>
+        <v>45971</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6859,7 +6849,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6902,7 +6892,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 56672-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6916,10 +6906,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44943</v>
+        <v>45975</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6932,7 +6922,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6975,7 +6965,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6989,10 +6979,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44895</v>
+        <v>45982</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7005,7 +6995,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7048,7 +7038,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7062,10 +7052,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44895</v>
+        <v>45817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7078,7 +7068,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7121,7 +7111,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7135,10 +7125,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44895</v>
+        <v>44700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7151,7 +7141,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7194,7 +7184,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7208,10 +7198,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45216</v>
+        <v>45170</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7224,7 +7214,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7267,7 +7257,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7281,10 +7271,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45392</v>
+        <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7297,7 +7287,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7340,7 +7330,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7354,10 +7344,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45817</v>
+        <v>46002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7370,7 +7360,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7413,7 +7403,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7427,10 +7417,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45587</v>
+        <v>46008</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7486,7 +7476,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7500,10 +7490,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45350</v>
+        <v>46008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7516,7 +7506,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7559,7 +7549,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 62757-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7573,10 +7563,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45971</v>
+        <v>46008</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7589,7 +7579,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7632,7 +7622,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56672-2025</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7646,10 +7636,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45975</v>
+        <v>45329</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7662,7 +7652,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7705,7 +7695,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7715,14 +7705,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45055</v>
+        <v>45441</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7735,7 +7725,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7778,7 +7768,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7792,10 +7782,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46245</v>
+        <v>45392</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7808,7 +7798,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7851,7 +7841,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7865,10 +7855,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45982</v>
+        <v>46034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7881,7 +7871,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7924,7 +7914,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7938,10 +7928,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45216</v>
+        <v>46036</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7997,7 +7987,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8007,14 +7997,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46206</v>
+        <v>44959</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8027,7 +8017,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8070,7 +8060,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8080,14 +8070,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44710</v>
+        <v>45726</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8100,7 +8090,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.9</v>
+        <v>0.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8143,7 +8133,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 23592-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8157,10 +8147,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44746</v>
+        <v>44721</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8173,7 +8163,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8216,7 +8206,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8230,10 +8220,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46002</v>
+        <v>45565</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8245,8 +8235,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8289,7 +8284,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8303,10 +8298,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46002</v>
+        <v>45476</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8319,7 +8314,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8362,7 +8357,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8376,10 +8371,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46008</v>
+        <v>45476</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8392,7 +8387,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8435,7 +8430,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8449,10 +8444,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46008</v>
+        <v>45350</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8465,7 +8460,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8508,7 +8503,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62757-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8518,14 +8513,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46008</v>
+        <v>44704</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8538,7 +8533,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8581,7 +8576,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8595,10 +8590,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45329</v>
+        <v>46245</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8611,7 +8606,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8654,7 +8649,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8668,10 +8663,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46276</v>
+        <v>46132</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8684,7 +8679,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>11.6</v>
+        <v>3.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8727,7 +8722,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8737,14 +8732,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45441</v>
+        <v>44712</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8757,7 +8752,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>23.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8800,7 +8795,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8814,10 +8809,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44700</v>
+        <v>45028</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8829,8 +8824,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8873,7 +8873,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44746</v>
+        <v>46206</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8946,7 +8946,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8956,14 +8956,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46034</v>
+        <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9019,7 +9019,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46036</v>
+        <v>44746</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9092,7 +9092,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9102,14 +9102,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44959</v>
+        <v>44710</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9165,7 +9165,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23592-2022</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9179,10 +9179,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44721</v>
+        <v>46276</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>11.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9248,14 +9248,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45726</v>
+        <v>45805</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9311,7 +9311,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45170</v>
+        <v>45812</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45300</v>
+        <v>45835</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9457,7 +9457,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45805</v>
+        <v>45835</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9530,7 +9530,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9540,14 +9540,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45812</v>
+        <v>45588</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>45539</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45968</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>44943</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44462</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>46008</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44487</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>44645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44712</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>44750</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>44532</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>45548</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45386</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45145</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45055</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44746</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44809</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>45216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45350</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>44746</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45216</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45216</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44828</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>45917</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45817</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45834</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>45589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45887</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>45723</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45919</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>45929</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>45931</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44805</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44943</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44970</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>45587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>45345</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45412</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>45971</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45975</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>45982</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>45170</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>46002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>46008</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>46008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>46008</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45329</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45441</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>45392</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>46034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>46036</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44959</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45726</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44721</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45565</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45476</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45476</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>45350</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>44704</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>46245</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46132</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44712</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>45028</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>46206</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>44746</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44710</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>46276</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>45805</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>45812</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>45835</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45835</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45588</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>45539</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE117"/>
+  <dimension ref="A1:AE115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45968</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>44943</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44462</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 62755-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45092</v>
+        <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2478,46 +2478,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 62755-2025</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46008</v>
+        <v>45092</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2583,39 +2583,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
         <v>45282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44487</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>44645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44712</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>44750</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>44532</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>45548</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45386</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45145</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45055</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>44746</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44809</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>45216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45350</v>
+        <v>44746</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44746</v>
+        <v>45350</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.6</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45216</v>
+        <v>45588</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4629,7 +4629,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45887</v>
+        <v>44712</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>23.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4712,14 +4712,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44828</v>
+        <v>45897</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45917</v>
+        <v>45216</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45817</v>
+        <v>45216</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45834</v>
+        <v>45917</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45589</v>
+        <v>45817</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5077,14 +5077,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45897</v>
+        <v>45834</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
         <v>45887</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45723</v>
+        <v>45589</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
         <v>45919</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45922</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5588,14 +5588,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45929</v>
+        <v>44828</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5661,14 +5661,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45931</v>
+        <v>45929</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5724,7 +5724,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44517</v>
+        <v>45723</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44895</v>
+        <v>45931</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5960,7 +5960,7 @@
         <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44805</v>
+        <v>44895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44943</v>
+        <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6162,7 +6162,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44517</v>
+        <v>44805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44517</v>
+        <v>44943</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44970</v>
+        <v>44895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45587</v>
+        <v>44895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6610,14 +6610,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45345</v>
+        <v>44970</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45412</v>
+        <v>45817</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>45971</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56672-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45975</v>
+        <v>45587</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6982,7 +6982,7 @@
         <v>45982</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7048,14 +7048,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45817</v>
+        <v>45345</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7111,7 +7111,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44700</v>
+        <v>45412</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45170</v>
+        <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7257,7 +7257,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7274,7 +7274,7 @@
         <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7330,7 +7330,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7403,7 +7403,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7420,7 +7420,7 @@
         <v>46008</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7476,7 +7476,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 62757-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7493,7 +7493,7 @@
         <v>46008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7549,7 +7549,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62757-2025</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46008</v>
+        <v>45329</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7622,7 +7622,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45329</v>
+        <v>46034</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7695,7 +7695,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45441</v>
+        <v>46036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7768,7 +7768,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45392</v>
+        <v>44700</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46034</v>
+        <v>45170</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7914,7 +7914,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46036</v>
+        <v>45726</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8001,10 +8001,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44959</v>
+        <v>45441</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8060,7 +8060,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8070,14 +8070,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45726</v>
+        <v>45392</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8133,7 +8133,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 23592-2022</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8143,14 +8143,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44721</v>
+        <v>44959</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8206,7 +8206,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8216,14 +8216,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45565</v>
+        <v>44704</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8235,13 +8235,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8284,7 +8279,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8298,10 +8293,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45476</v>
+        <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8314,7 +8309,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8357,7 +8352,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8371,10 +8366,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45476</v>
+        <v>46132</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8387,7 +8382,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8430,7 +8425,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8444,10 +8439,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45350</v>
+        <v>45565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8459,8 +8454,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8513,14 +8513,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44704</v>
+        <v>45476</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46245</v>
+        <v>45476</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8649,7 +8649,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46132</v>
+        <v>45350</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8722,7 +8722,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44712</v>
+        <v>45028</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8751,8 +8751,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>23.3</v>
+        <v>4.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8795,7 +8800,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8809,10 +8814,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45028</v>
+        <v>46276</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8824,13 +8829,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>4.5</v>
+        <v>11.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8873,7 +8873,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8883,14 +8883,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46206</v>
+        <v>45300</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8946,7 +8946,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8956,14 +8956,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45300</v>
+        <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9019,7 +9019,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44746</v>
+        <v>46245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9109,7 +9109,7 @@
         <v>44710</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9179,10 +9179,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46276</v>
+        <v>45805</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11.6</v>
+        <v>4.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9248,14 +9248,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45805</v>
+        <v>45812</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9311,7 +9311,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45812</v>
+        <v>45835</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9401,7 +9401,7 @@
         <v>45835</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9457,24 +9457,24 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>S 3456-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45835</v>
+        <v>45539</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9527,27 +9527,27 @@
       </c>
       <c r="V114" s="2" t="inlineStr"/>
     </row>
-    <row r="115" ht="15" customHeight="1">
+    <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>S 3064-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45588</v>
+        <v>45517</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9599,152 +9599,6 @@
         <v>0</v>
       </c>
       <c r="V115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>S 3456-2024</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="n">
-        <v>45539</v>
-      </c>
-      <c r="E116" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I116" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>S 3064-2024</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="n">
-        <v>45517</v>
-      </c>
-      <c r="E117" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I117" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE115"/>
+  <dimension ref="A1:AE113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,144 +1108,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45968</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 58073-2025</t>
+          <t>A 2447-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45982</v>
+        <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1526,146 +1526,146 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2447-2023 artfynd.xlsx", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2447-2023 karta.png", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2447-2023 georefererad karta.tif", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2447-2023 FSC-klagomål.docx", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2447-2023 FSC-klagomål mail.docx", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2447-2023 tillsynsbegäran.docx", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2447-2023 tillsynsbegäran mail.docx", "A 2447-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 58073-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Kambräken</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 58073-2025 artfynd.xlsx", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 58073-2025 karta.png", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 58073-2025 georefererad karta.tif", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 58073-2025 FSC-klagomål.docx", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 58073-2025 FSC-klagomål mail.docx", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 58073-2025 tillsynsbegäran.docx", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 58073-2025 tillsynsbegäran mail.docx", "A 58073-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 2447-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Dolkstekelsglasvinge
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2447-2023 artfynd.xlsx", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2447-2023 karta.png", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2447-2023 georefererad karta.tif", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2447-2023 FSC-klagomål.docx", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2447-2023 FSC-klagomål mail.docx", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2447-2023 tillsynsbegäran.docx", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2447-2023 tillsynsbegäran mail.docx", "A 2447-2023")</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44623</v>
+        <v>45057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1953,39 +1953,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
         <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51900-2021</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44462</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2268,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2276,38 +2276,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 51900-2021 artfynd.xlsx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 51900-2021 karta.png", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 51900-2021 georefererad karta.tif", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 51900-2021 FSC-klagomål.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 51900-2021 FSC-klagomål mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 51900-2021 tillsynsbegäran.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 51900-2021 tillsynsbegäran mail.docx", "A 51900-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45057</v>
+        <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2377,42 +2377,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62755-2025</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46008</v>
+        <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2482,42 +2482,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 62755-2025 artfynd.xlsx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 62755-2025 karta.png", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 62755-2025 georefererad karta.tif", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 62755-2025 FSC-klagomål.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 62755-2025 FSC-klagomål mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 62755-2025 tillsynsbegäran.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 62755-2025 tillsynsbegäran mail.docx", "A 62755-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 33922-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2531,10 +2535,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45092</v>
+        <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2547,13 +2551,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2577,52 +2581,20 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Svart jordtunga</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 72415-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2632,14 +2604,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45282</v>
+        <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2652,10 +2624,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2682,56 +2654,20 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
+      <c r="V21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33922-2022</t>
+          <t>A 58025-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2745,10 +2681,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44790</v>
+        <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2761,7 +2697,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2804,7 +2740,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 72415-2021</t>
+          <t>A 30197-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2814,14 +2750,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44545</v>
+        <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2834,7 +2770,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2877,7 +2813,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58025-2021</t>
+          <t>A 29106-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2891,10 +2827,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44487</v>
+        <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2907,7 +2843,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>9.1</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2950,7 +2886,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30197-2022</t>
+          <t>A 20681-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2964,10 +2900,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44757</v>
+        <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2980,7 +2916,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3023,7 +2959,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29106-2022</t>
+          <t>A 13411-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3037,10 +2973,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44750</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3053,7 +2989,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3096,7 +3032,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20681-2022</t>
+          <t>A 468-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3106,14 +3042,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44700</v>
+        <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3126,7 +3062,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3169,7 +3105,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13411-2022</t>
+          <t>A 22240-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3183,10 +3119,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44645</v>
+        <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3199,7 +3135,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3242,7 +3178,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 468-2022</t>
+          <t>A 15138-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3252,14 +3188,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44566</v>
+        <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3315,7 +3251,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22240-2022</t>
+          <t>A 52777-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3325,14 +3261,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44712</v>
+        <v>44467</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3345,7 +3281,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3388,7 +3324,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15138-2022</t>
+          <t>A 29101-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3402,10 +3338,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44658</v>
+        <v>44750</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3418,7 +3354,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3461,7 +3397,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 52777-2021</t>
+          <t>A 69614-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3471,14 +3407,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44467</v>
+        <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3491,7 +3427,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29101-2022</t>
+          <t>A 69628-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3548,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44750</v>
+        <v>44532</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3564,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3607,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 69614-2021</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3621,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44532</v>
+        <v>45350</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3637,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3680,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 69628-2021</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3694,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44532</v>
+        <v>45412</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3710,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3753,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3767,10 +3703,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45217</v>
+        <v>44746</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3783,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3826,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3836,14 +3772,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45548</v>
+        <v>45345</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3856,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3899,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3909,14 +3845,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45386</v>
+        <v>45217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3972,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3982,14 +3918,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45145</v>
+        <v>45216</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4045,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4059,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45055</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4118,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4132,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44746</v>
+        <v>44809</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4191,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4205,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44809</v>
+        <v>44828</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4264,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4278,10 +4214,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4337,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4351,10 +4287,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44746</v>
+        <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4410,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4424,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45350</v>
+        <v>45392</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4483,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4493,14 +4429,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4556,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4570,10 +4506,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45588</v>
+        <v>45587</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4629,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4643,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44712</v>
+        <v>45350</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>23.3</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4702,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4712,14 +4648,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45897</v>
+        <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4775,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4789,10 +4725,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45216</v>
+        <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4848,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4858,14 +4794,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45216</v>
+        <v>45919</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4921,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4935,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45917</v>
+        <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4994,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5008,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45817</v>
+        <v>45805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5067,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5081,10 +5017,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45834</v>
+        <v>45476</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5140,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5154,10 +5090,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45887</v>
+        <v>45476</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5213,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5223,14 +5159,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45589</v>
+        <v>45929</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5243,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5286,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5296,14 +5232,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5316,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5359,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5373,10 +5309,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45922</v>
+        <v>44895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5389,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5432,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5446,10 +5382,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45922</v>
+        <v>44517</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5462,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5505,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5519,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45922</v>
+        <v>44517</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5535,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5578,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5588,14 +5524,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44828</v>
+        <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5608,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5651,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5661,14 +5597,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45929</v>
+        <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5681,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.699999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5724,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5738,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45723</v>
+        <v>44805</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5797,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5811,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45931</v>
+        <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5827,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5870,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5884,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44517</v>
+        <v>44970</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5900,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5943,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5957,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5973,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6033,7 +5969,7 @@
         <v>44895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6106,7 +6042,7 @@
         <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6162,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6176,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44805</v>
+        <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6192,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6235,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6249,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44943</v>
+        <v>45548</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6265,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6308,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6318,14 +6254,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44517</v>
+        <v>45145</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6338,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6381,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6395,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44517</v>
+        <v>45055</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6411,7 +6347,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6454,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6468,10 +6404,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44895</v>
+        <v>45971</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6484,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6527,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6541,10 +6477,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44895</v>
+        <v>45565</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6556,8 +6492,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6600,7 +6541,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6614,10 +6555,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44970</v>
+        <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6630,7 +6571,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6673,7 +6614,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6687,10 +6628,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>45982</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6703,7 +6644,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6746,7 +6687,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6760,10 +6701,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45817</v>
+        <v>45028</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6775,8 +6716,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6819,7 +6765,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6829,14 +6775,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45971</v>
+        <v>45386</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6849,7 +6795,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6892,7 +6838,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6906,10 +6852,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45587</v>
+        <v>44710</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6922,7 +6868,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6965,7 +6911,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6979,10 +6925,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45982</v>
+        <v>44746</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6995,7 +6941,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7038,7 +6984,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7048,14 +6994,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45345</v>
+        <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7068,7 +7014,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7111,7 +7057,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7125,10 +7071,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45412</v>
+        <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7141,7 +7087,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7184,7 +7130,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7198,10 +7144,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46002</v>
+        <v>46034</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7214,7 +7160,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7257,7 +7203,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7271,10 +7217,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46002</v>
+        <v>46036</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7287,7 +7233,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7347,7 +7293,7 @@
         <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7420,7 +7366,7 @@
         <v>46008</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7493,7 +7439,7 @@
         <v>46008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7549,7 +7495,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7563,10 +7509,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45329</v>
+        <v>45835</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7579,7 +7525,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7622,7 +7568,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7636,10 +7582,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46034</v>
+        <v>45835</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7652,7 +7598,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7695,7 +7641,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7709,10 +7655,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46036</v>
+        <v>45329</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7725,7 +7671,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7768,7 +7714,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7778,14 +7724,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44700</v>
+        <v>45726</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7798,7 +7744,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7841,7 +7787,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7851,14 +7797,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45170</v>
+        <v>45441</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7871,7 +7817,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7914,7 +7860,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7924,14 +7870,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45726</v>
+        <v>46245</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7944,7 +7890,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7987,7 +7933,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7997,14 +7943,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45441</v>
+        <v>44700</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8017,7 +7963,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8060,7 +8006,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8074,10 +8020,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45392</v>
+        <v>44746</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8090,7 +8036,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8133,7 +8079,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8143,14 +8089,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44959</v>
+        <v>44704</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8163,7 +8109,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8206,7 +8152,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8216,14 +8162,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44704</v>
+        <v>46132</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8236,7 +8182,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8279,7 +8225,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8289,14 +8235,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46206</v>
+        <v>44959</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8309,7 +8255,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8352,7 +8298,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8366,10 +8312,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46132</v>
+        <v>45170</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8382,7 +8328,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8425,7 +8371,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8439,10 +8385,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45565</v>
+        <v>45588</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8454,13 +8400,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8503,7 +8444,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8517,10 +8458,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45476</v>
+        <v>45723</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8533,7 +8474,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8576,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8590,10 +8531,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45476</v>
+        <v>44712</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8606,7 +8547,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>23.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8649,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8663,10 +8604,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45350</v>
+        <v>45917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8679,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8722,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8732,14 +8673,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45028</v>
+        <v>45300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8751,13 +8692,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8800,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8814,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46276</v>
+        <v>45834</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8830,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>11.6</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8873,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8883,14 +8819,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45300</v>
+        <v>45817</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8903,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8946,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8960,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44746</v>
+        <v>45589</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8976,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9019,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9033,10 +8969,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46245</v>
+        <v>45216</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9049,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9092,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9106,10 +9042,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44710</v>
+        <v>45817</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9122,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9165,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9179,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45805</v>
+        <v>46206</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9195,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9238,7 +9174,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9248,14 +9184,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45812</v>
+        <v>46276</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9268,7 +9204,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>11.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9311,24 +9247,24 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>S 3456-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45835</v>
+        <v>45539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9341,7 +9277,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9381,27 +9317,27 @@
       </c>
       <c r="V112" s="2" t="inlineStr"/>
     </row>
-    <row r="113" ht="15" customHeight="1">
+    <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>S 3064-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45835</v>
+        <v>45517</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9414,7 +9350,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9453,152 +9389,6 @@
         <v>0</v>
       </c>
       <c r="V113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114" ht="15" customHeight="1">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>S 3456-2024</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="n">
-        <v>45539</v>
-      </c>
-      <c r="E114" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I114" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="n">
-        <v>0</v>
-      </c>
-      <c r="T114" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" t="n">
-        <v>0</v>
-      </c>
-      <c r="V114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>S 3064-2024</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="n">
-        <v>45517</v>
-      </c>
-      <c r="E115" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I115" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,257 +1104,36 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45968</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2447-2023</t>
+          <t>A 58073-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44943</v>
+        <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1526,146 +1526,146 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 58073-2025 artfynd.xlsx", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 58073-2025 karta.png", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 58073-2025 georefererad karta.tif", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 58073-2025 FSC-klagomål.docx", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 58073-2025 FSC-klagomål mail.docx", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 58073-2025 tillsynsbegäran.docx", "A 58073-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 58073-2025 tillsynsbegäran mail.docx", "A 58073-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 2447-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Dolkstekelsglasvinge
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2447-2023 artfynd.xlsx", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2447-2023 karta.png", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2447-2023 georefererad karta.tif", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2447-2023 FSC-klagomål.docx", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2447-2023 FSC-klagomål mail.docx", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2447-2023 tillsynsbegäran.docx", "A 2447-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2447-2023 tillsynsbegäran mail.docx", "A 2447-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 58073-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45982</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Kambräken</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 58073-2025 artfynd.xlsx", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 58073-2025 karta.png", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 58073-2025 georefererad karta.tif", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 58073-2025 FSC-klagomål.docx", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 58073-2025 FSC-klagomål mail.docx", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 58073-2025 tillsynsbegäran.docx", "A 58073-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 58073-2025 tillsynsbegäran mail.docx", "A 58073-2025")</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45057</v>
+        <v>44623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1953,39 +1953,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
         <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44623</v>
+        <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2268,39 +2268,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44467</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44750</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44532</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45350</v>
+        <v>45217</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45412</v>
+        <v>45548</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44746</v>
+        <v>45386</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45345</v>
+        <v>45145</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45217</v>
+        <v>45055</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45216</v>
+        <v>44746</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>44809</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44809</v>
+        <v>45216</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44828</v>
+        <v>44746</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45887</v>
+        <v>45350</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4290,7 +4290,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45392</v>
+        <v>45588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4429,14 +4429,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45897</v>
+        <v>44712</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>23.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45587</v>
+        <v>45897</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45350</v>
+        <v>45216</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45922</v>
+        <v>45216</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45922</v>
+        <v>45887</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4801,7 +4801,7 @@
         <v>45919</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45922</v>
+        <v>44828</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45805</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45476</v>
+        <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45476</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>45929</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45931</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5514,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5524,14 +5524,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45812</v>
+        <v>44895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44517</v>
+        <v>44805</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44805</v>
+        <v>44943</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44895</v>
+        <v>45917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44970</v>
+        <v>44517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44943</v>
+        <v>44517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5969,7 +5969,7 @@
         <v>44895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6042,7 +6042,7 @@
         <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44895</v>
+        <v>44970</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45548</v>
+        <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6254,14 +6254,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45145</v>
+        <v>45834</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45055</v>
+        <v>45589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45971</v>
+        <v>45723</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45565</v>
+        <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6492,13 +6492,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6541,7 +6536,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6555,10 +6550,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45216</v>
+        <v>45587</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6571,7 +6566,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6624,14 +6619,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45982</v>
+        <v>45345</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6644,7 +6639,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6687,7 +6682,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6701,10 +6696,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45028</v>
+        <v>45982</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6716,13 +6711,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6765,7 +6755,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6775,14 +6765,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45386</v>
+        <v>45412</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6795,7 +6785,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6838,7 +6828,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6852,10 +6842,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44710</v>
+        <v>45216</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6868,7 +6858,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6911,7 +6901,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6925,10 +6915,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44746</v>
+        <v>46002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6941,7 +6931,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7001,7 +6991,7 @@
         <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7057,7 +7047,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7071,10 +7061,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7087,7 +7077,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7130,7 +7120,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7144,10 +7134,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46034</v>
+        <v>46008</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7160,7 +7150,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7203,7 +7193,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 62757-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7217,10 +7207,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46036</v>
+        <v>46008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7233,7 +7223,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7276,7 +7266,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7290,10 +7280,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46008</v>
+        <v>45329</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7306,7 +7296,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7349,7 +7339,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7363,10 +7353,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46008</v>
+        <v>45817</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7379,7 +7369,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7422,7 +7412,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62757-2025</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7436,10 +7426,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46008</v>
+        <v>46034</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7452,7 +7442,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7495,7 +7485,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7509,10 +7499,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45835</v>
+        <v>46036</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7525,7 +7515,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7568,7 +7558,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7582,10 +7572,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45835</v>
+        <v>44700</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7598,7 +7588,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7641,7 +7631,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7655,10 +7645,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45329</v>
+        <v>45170</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7671,7 +7661,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7731,7 +7721,7 @@
         <v>45726</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7804,7 +7794,7 @@
         <v>45441</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7860,7 +7850,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7874,10 +7864,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46245</v>
+        <v>45392</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7890,7 +7880,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7933,7 +7923,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7943,14 +7933,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44700</v>
+        <v>44959</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7963,7 +7953,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8006,7 +7996,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8016,14 +8006,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44746</v>
+        <v>44704</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8036,7 +8026,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8079,7 +8069,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8089,14 +8079,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44704</v>
+        <v>46132</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8109,7 +8099,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8152,7 +8142,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8166,10 +8156,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46132</v>
+        <v>45565</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8181,8 +8171,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8225,7 +8220,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8235,14 +8230,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44959</v>
+        <v>45476</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8255,7 +8250,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8298,7 +8293,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8312,10 +8307,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45170</v>
+        <v>45476</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8328,7 +8323,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8371,7 +8366,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8385,10 +8380,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45588</v>
+        <v>46206</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8444,7 +8439,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8458,10 +8453,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45723</v>
+        <v>45350</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8474,7 +8469,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8517,7 +8512,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8531,10 +8526,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44712</v>
+        <v>45028</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8546,8 +8541,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>23.3</v>
+        <v>4.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8600,14 +8600,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45917</v>
+        <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8673,14 +8673,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45300</v>
+        <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45834</v>
+        <v>46276</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>11.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45817</v>
+        <v>44710</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45589</v>
+        <v>46245</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8969,10 +8969,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45216</v>
+        <v>45805</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9038,14 +9038,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45817</v>
+        <v>45812</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46206</v>
+        <v>45835</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9174,7 +9174,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9188,10 +9188,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46276</v>
+        <v>45835</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>11.6</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9264,7 +9264,7 @@
         <v>45539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45517</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,151 +1108,39 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 22268-2022</t>
+          <t>A 55111-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44712</v>
+        <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>16.6</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1206,148 +1206,148 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Stor revmossa
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 22268-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Havstulpanlav
 Stubbspretmossa
 Mattlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 55111-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Stor revmossa
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 58073-2025</t>
+          <t>A 2447-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45982</v>
+        <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1526,146 +1526,146 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2447-2023 artfynd.xlsx", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2447-2023 karta.png", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2447-2023 georefererad karta.tif", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2447-2023 FSC-klagomål.docx", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2447-2023 FSC-klagomål mail.docx", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2447-2023 tillsynsbegäran.docx", "A 2447-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2447-2023 tillsynsbegäran mail.docx", "A 2447-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 58073-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Kambräken</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 58073-2025 artfynd.xlsx", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 58073-2025 karta.png", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 58073-2025 georefererad karta.tif", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 58073-2025 FSC-klagomål.docx", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 58073-2025 FSC-klagomål mail.docx", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 58073-2025 tillsynsbegäran.docx", "A 58073-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 58073-2025 tillsynsbegäran mail.docx", "A 58073-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 2447-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Dolkstekelsglasvinge
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2447-2023 artfynd.xlsx", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2447-2023 karta.png", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2447-2023 georefererad karta.tif", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2447-2023 FSC-klagomål.docx", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2447-2023 FSC-klagomål mail.docx", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2447-2023 tillsynsbegäran.docx", "A 2447-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2447-2023 tillsynsbegäran mail.docx", "A 2447-2023")</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44623</v>
+        <v>45282</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1957,35 +1957,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
@@ -2009,7 +2013,7 @@
         <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2118,7 @@
         <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2202,7 +2206,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2220,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45057</v>
+        <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,7 +2236,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2272,42 +2276,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2325,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45092</v>
+        <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,7 +2341,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2377,42 +2381,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,10 +2430,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45282</v>
+        <v>44623</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2442,7 +2446,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2482,39 +2486,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44467</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44750</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44532</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45217</v>
+        <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45548</v>
+        <v>45350</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45386</v>
+        <v>45345</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3772,14 +3772,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45145</v>
+        <v>45217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45055</v>
+        <v>45412</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44746</v>
+        <v>45216</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44809</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45216</v>
+        <v>44828</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44746</v>
+        <v>45329</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45350</v>
+        <v>46034</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45588</v>
+        <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44712</v>
+        <v>46036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>23.3</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>45897</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45216</v>
+        <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45216</v>
+        <v>45476</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4721,14 +4721,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45887</v>
+        <v>45726</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4794,14 +4794,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44828</v>
+        <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45919</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>45548</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5093,7 +5093,7 @@
         <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45929</v>
+        <v>45145</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5232,14 +5232,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45931</v>
+        <v>45929</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44517</v>
+        <v>45805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44895</v>
+        <v>45931</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5458,7 +5458,7 @@
         <v>44895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5514,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44805</v>
+        <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44943</v>
+        <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45917</v>
+        <v>44805</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44517</v>
+        <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6042,7 +6042,7 @@
         <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44970</v>
+        <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45817</v>
+        <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6254,14 +6254,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45834</v>
+        <v>45812</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45589</v>
+        <v>45565</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6346,8 +6346,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6390,7 +6395,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6400,14 +6405,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45723</v>
+        <v>44704</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6420,7 +6425,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6480,7 +6485,7 @@
         <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6536,7 +6541,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6550,10 +6555,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45587</v>
+        <v>46132</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6566,7 +6571,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6609,7 +6614,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6619,14 +6624,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45345</v>
+        <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6638,8 +6643,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6682,7 +6692,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6692,14 +6702,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45982</v>
+        <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6712,7 +6722,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6755,7 +6765,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6769,10 +6779,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45412</v>
+        <v>45982</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6785,7 +6795,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6828,7 +6838,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6842,10 +6852,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45216</v>
+        <v>45723</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6858,7 +6868,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6901,7 +6911,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6915,10 +6925,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46002</v>
+        <v>44712</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6931,7 +6941,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>23.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6991,7 +7001,7 @@
         <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7047,7 +7057,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7061,10 +7071,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7077,7 +7087,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7120,7 +7130,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46008</v>
+        <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7150,7 +7160,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7193,7 +7203,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62757-2025</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7210,7 +7220,7 @@
         <v>46008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7223,7 +7233,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7266,7 +7276,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7280,10 +7290,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45329</v>
+        <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7296,7 +7306,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7339,7 +7349,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7353,10 +7363,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45817</v>
+        <v>45834</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7369,7 +7379,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7412,7 +7422,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7426,10 +7436,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46034</v>
+        <v>45817</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7442,7 +7452,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7485,7 +7495,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7499,10 +7509,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46036</v>
+        <v>45589</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7558,7 +7568,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7572,10 +7582,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44700</v>
+        <v>44809</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7588,7 +7598,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7631,7 +7641,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7645,10 +7655,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45170</v>
+        <v>45216</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7661,7 +7671,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7704,7 +7714,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7714,14 +7724,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45726</v>
+        <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7734,7 +7744,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7777,7 +7787,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7787,14 +7797,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45441</v>
+        <v>45835</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7807,7 +7817,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7850,7 +7860,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7864,10 +7874,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45392</v>
+        <v>45817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7880,7 +7890,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7923,7 +7933,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7933,14 +7943,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44959</v>
+        <v>45392</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7953,7 +7963,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7996,7 +8006,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8006,14 +8016,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44704</v>
+        <v>45587</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8026,7 +8036,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8069,7 +8079,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8083,10 +8093,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46132</v>
+        <v>45350</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8099,7 +8109,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8142,7 +8152,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8156,10 +8166,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45565</v>
+        <v>45588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8171,13 +8181,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8220,7 +8225,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8234,10 +8239,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45476</v>
+        <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8250,7 +8255,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8293,7 +8298,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8307,10 +8312,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45476</v>
+        <v>45055</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8323,7 +8328,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8366,7 +8371,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8380,10 +8385,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46206</v>
+        <v>45216</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8396,7 +8401,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8439,7 +8444,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8453,10 +8458,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45350</v>
+        <v>44710</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8469,7 +8474,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8512,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8526,10 +8531,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45028</v>
+        <v>44746</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8541,13 +8546,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8600,14 +8600,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45300</v>
+        <v>46276</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8673,14 +8673,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44746</v>
+        <v>45441</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46276</v>
+        <v>46245</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44710</v>
+        <v>44700</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46245</v>
+        <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8969,10 +8969,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45805</v>
+        <v>46290</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45812</v>
+        <v>44959</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45835</v>
+        <v>45170</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9174,7 +9174,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9184,14 +9184,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45835</v>
+        <v>45300</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9264,7 +9264,7 @@
         <v>45539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45517</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>44746</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44943</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>45282</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44623</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44467</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44750</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44532</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45350</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45345</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45412</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45216</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44828</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45329</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>46034</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45897</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45476</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45726</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45919</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45548</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45145</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45929</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45931</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>44895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>44517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44805</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45812</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45565</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44704</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>46132</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45982</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45723</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44712</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>46008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45834</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45817</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45589</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44809</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>45216</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>45835</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45392</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45587</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>45350</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>45588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45055</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45216</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44710</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44746</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>46276</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45441</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46245</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44700</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>46290</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44959</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45170</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45300</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45517</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>44746</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44943</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>45282</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44623</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44467</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44750</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44532</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45350</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45345</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45412</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45216</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44828</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45329</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>46034</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45897</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45476</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45726</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45919</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45548</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45145</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45929</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45931</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>44895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>44517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44805</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45812</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45565</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44704</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>46132</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45982</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45723</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44712</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>46008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45834</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45817</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45589</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44809</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>45216</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>45835</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45392</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45587</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>45350</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>45588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45055</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45216</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44710</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44746</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>46276</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45441</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46245</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44700</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>46290</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44959</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45170</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45300</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45517</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE113"/>
+  <dimension ref="A1:AE112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,257 +1104,36 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45282</v>
+        <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1953,50 +1953,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2010,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2026,13 +2022,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2059,49 +2055,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2115,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44943</v>
+        <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2131,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2164,49 +2160,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2220,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45092</v>
+        <v>45282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2236,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2272,39 +2268,43 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
         <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2482,39 +2482,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52777-2021</t>
+          <t>A 29101-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44467</v>
+        <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29101-2022</t>
+          <t>A 69614-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44750</v>
+        <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 69614-2021</t>
+          <t>A 69628-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 69628-2021</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44532</v>
+        <v>45217</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44746</v>
+        <v>45548</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45350</v>
+        <v>46002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45345</v>
+        <v>45887</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45217</v>
+        <v>46002</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45412</v>
+        <v>46008</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45216</v>
+        <v>46008</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44828</v>
+        <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4137,14 +4137,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45329</v>
+        <v>45897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.9</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46034</v>
+        <v>45805</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45887</v>
+        <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4356,14 +4356,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45887</v>
+        <v>45812</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4429,14 +4429,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46036</v>
+        <v>45919</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45897</v>
+        <v>45922</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45476</v>
+        <v>45922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45476</v>
+        <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4721,14 +4721,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45726</v>
+        <v>45329</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>6.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4794,14 +4794,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45922</v>
+        <v>45929</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45922</v>
+        <v>45055</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45548</v>
+        <v>44517</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5159,14 +5159,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45145</v>
+        <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5232,14 +5232,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45929</v>
+        <v>44895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45805</v>
+        <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45931</v>
+        <v>44943</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>44517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44517</v>
+        <v>45835</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44805</v>
+        <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44895</v>
+        <v>45835</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44943</v>
+        <v>44746</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44895</v>
+        <v>46034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44895</v>
+        <v>44809</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44895</v>
+        <v>45588</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6254,14 +6254,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45812</v>
+        <v>45971</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45565</v>
+        <v>46036</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6346,13 +6346,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6395,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6405,14 +6400,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44704</v>
+        <v>45216</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6425,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6468,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6498,7 +6493,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6541,7 +6536,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6555,10 +6550,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46132</v>
+        <v>44746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6571,7 +6566,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45028</v>
+        <v>45350</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6643,13 +6638,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6692,7 +6682,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6702,14 +6692,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45386</v>
+        <v>45216</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6722,7 +6712,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6765,7 +6755,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6779,10 +6769,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45982</v>
+        <v>45216</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6795,7 +6785,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6838,7 +6828,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6848,14 +6838,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6868,7 +6858,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6911,7 +6901,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6925,10 +6915,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44712</v>
+        <v>44828</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6941,7 +6931,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>23.3</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6984,7 +6974,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6998,10 +6988,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46002</v>
+        <v>45587</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7014,7 +7004,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7057,7 +7047,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7067,14 +7057,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46002</v>
+        <v>44704</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7087,7 +7077,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7130,7 +7120,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7140,14 +7130,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45917</v>
+        <v>45345</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7160,7 +7150,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7203,7 +7193,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7217,10 +7207,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46008</v>
+        <v>46132</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7233,7 +7223,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7276,7 +7266,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7290,10 +7280,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46008</v>
+        <v>45412</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7306,7 +7296,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7349,7 +7339,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7363,10 +7353,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45834</v>
+        <v>44712</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7379,7 +7369,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>23.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7422,7 +7412,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7436,10 +7426,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45817</v>
+        <v>45917</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7452,7 +7442,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7495,7 +7485,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7509,10 +7499,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45589</v>
+        <v>45817</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7525,7 +7515,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7568,7 +7558,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7582,10 +7572,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44809</v>
+        <v>45834</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7598,7 +7588,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7641,7 +7631,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7655,10 +7645,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45216</v>
+        <v>45589</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7671,7 +7661,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7714,7 +7704,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7728,10 +7718,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45835</v>
+        <v>45723</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7744,7 +7734,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7787,7 +7777,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7801,10 +7791,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45835</v>
+        <v>44700</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7817,7 +7807,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7860,7 +7850,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7874,10 +7864,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45817</v>
+        <v>45170</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7890,7 +7880,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7933,7 +7923,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7947,10 +7937,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45392</v>
+        <v>45216</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7963,7 +7953,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8006,7 +7996,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8016,14 +8006,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45587</v>
+        <v>45441</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8036,7 +8026,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8079,7 +8069,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8093,10 +8083,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45350</v>
+        <v>45817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8109,7 +8099,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8152,7 +8142,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8166,10 +8156,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45588</v>
+        <v>45392</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8182,7 +8172,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8225,7 +8215,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8235,14 +8225,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46206</v>
+        <v>44959</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8255,7 +8245,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8298,7 +8288,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8312,10 +8302,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45055</v>
+        <v>45565</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8327,8 +8317,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8371,7 +8366,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8385,10 +8380,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45216</v>
+        <v>45476</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8401,7 +8396,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8444,7 +8439,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8458,10 +8453,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44710</v>
+        <v>45476</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8474,7 +8469,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8517,7 +8512,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8531,10 +8526,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44746</v>
+        <v>45350</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8547,7 +8542,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8585,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8604,10 +8599,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46276</v>
+        <v>46206</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8615,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>11.6</v>
+        <v>3.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8658,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8673,14 +8668,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45441</v>
+        <v>45028</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8692,8 +8687,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8746,14 +8746,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46245</v>
+        <v>45300</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44700</v>
+        <v>44746</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44746</v>
+        <v>44710</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8969,10 +8969,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46290</v>
+        <v>46276</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7.3</v>
+        <v>11.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9038,14 +9038,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44959</v>
+        <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45170</v>
+        <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9174,24 +9174,24 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>S 3456-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45300</v>
+        <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9244,10 +9244,10 @@
       </c>
       <c r="V111" s="2" t="inlineStr"/>
     </row>
-    <row r="112" ht="15" customHeight="1">
+    <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 3456-2024</t>
+          <t>S 3064-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9261,10 +9261,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45539</v>
+        <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9316,79 +9316,6 @@
         <v>0</v>
       </c>
       <c r="V112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>S 3064-2024</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="n">
-        <v>45517</v>
-      </c>
-      <c r="E113" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I113" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,144 +1108,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2163,46 +2163,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45282</v>
+        <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2268,50 +2268,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2325,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45057</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2341,13 +2337,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2377,46 +2373,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2430,10 +2426,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45092</v>
+        <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2446,13 +2442,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2482,39 +2478,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45217</v>
+        <v>44746</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45548</v>
+        <v>45345</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46002</v>
+        <v>45217</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45887</v>
+        <v>45350</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46002</v>
+        <v>45216</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46008</v>
+        <v>45412</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45887</v>
+        <v>44828</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45386</v>
+        <v>45329</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4137,14 +4137,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45897</v>
+        <v>45887</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45805</v>
+        <v>45887</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45145</v>
+        <v>45897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4356,14 +4356,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45812</v>
+        <v>45805</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45919</v>
+        <v>45812</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45922</v>
+        <v>46034</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45922</v>
+        <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45922</v>
+        <v>45476</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45329</v>
+        <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4794,14 +4794,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45929</v>
+        <v>45548</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45055</v>
+        <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45931</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44517</v>
+        <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44895</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44895</v>
+        <v>45835</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44895</v>
+        <v>45835</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44805</v>
+        <v>45145</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5378,14 +5378,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44943</v>
+        <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44517</v>
+        <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5514,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45835</v>
+        <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45835</v>
+        <v>44805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44970</v>
+        <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44746</v>
+        <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46034</v>
+        <v>44943</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44809</v>
+        <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45588</v>
+        <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45971</v>
+        <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46036</v>
+        <v>45565</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6346,8 +6346,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6390,7 +6395,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6400,14 +6405,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45216</v>
+        <v>45726</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6420,7 +6425,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6463,7 +6468,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6477,10 +6482,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45982</v>
+        <v>45588</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6493,7 +6498,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6536,7 +6541,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6550,10 +6555,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44746</v>
+        <v>45971</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6566,7 +6571,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6609,7 +6614,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6623,10 +6628,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45350</v>
+        <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6638,8 +6643,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6682,7 +6692,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6692,14 +6702,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45216</v>
+        <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6712,7 +6722,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6755,7 +6765,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6769,10 +6779,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45216</v>
+        <v>45982</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6785,7 +6795,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6828,7 +6838,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6838,14 +6848,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45726</v>
+        <v>46002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6858,7 +6868,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6901,7 +6911,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6915,10 +6925,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44828</v>
+        <v>46002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6931,7 +6941,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6974,7 +6984,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6988,10 +6998,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45587</v>
+        <v>46008</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7047,7 +7057,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7057,14 +7067,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44704</v>
+        <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7077,7 +7087,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7120,7 +7130,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7130,14 +7140,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45345</v>
+        <v>44809</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7150,7 +7160,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7193,7 +7203,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7203,14 +7213,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46132</v>
+        <v>44704</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7223,7 +7233,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7266,7 +7276,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7280,10 +7290,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45412</v>
+        <v>46132</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7296,7 +7306,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7339,7 +7349,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7353,10 +7363,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44712</v>
+        <v>45392</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7369,7 +7379,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>23.3</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7412,7 +7422,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7426,10 +7436,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45917</v>
+        <v>45587</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7442,7 +7452,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7485,7 +7495,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7499,10 +7509,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45817</v>
+        <v>45723</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7515,7 +7525,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7558,7 +7568,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7572,10 +7582,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45834</v>
+        <v>44712</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7588,7 +7598,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>23.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7631,7 +7641,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7645,10 +7655,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45589</v>
+        <v>45917</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7661,7 +7671,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7704,7 +7714,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7718,10 +7728,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45723</v>
+        <v>45350</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7734,7 +7744,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7777,7 +7787,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7791,10 +7801,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44700</v>
+        <v>45834</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7807,7 +7817,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7850,7 +7860,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7864,10 +7874,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45170</v>
+        <v>45817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7880,7 +7890,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7923,7 +7933,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7937,10 +7947,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45216</v>
+        <v>45589</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7953,7 +7963,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7996,7 +8006,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8006,14 +8016,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45441</v>
+        <v>45216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8026,7 +8036,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8069,7 +8079,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8083,10 +8093,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45817</v>
+        <v>45055</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8099,7 +8109,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8142,7 +8152,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8156,10 +8166,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45392</v>
+        <v>45817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8172,7 +8182,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8215,7 +8225,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8225,14 +8235,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44959</v>
+        <v>45216</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8245,7 +8255,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8288,7 +8298,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8302,10 +8312,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45565</v>
+        <v>44710</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8317,13 +8327,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8366,7 +8371,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8380,10 +8385,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45476</v>
+        <v>44746</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8396,7 +8401,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8439,7 +8444,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8449,14 +8454,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45476</v>
+        <v>45441</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8469,7 +8474,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8512,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8526,10 +8531,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45350</v>
+        <v>46206</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8542,7 +8547,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8585,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8599,10 +8604,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46206</v>
+        <v>44700</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8615,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8658,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8672,10 +8677,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45028</v>
+        <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8687,13 +8692,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45300</v>
+        <v>44959</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44746</v>
+        <v>45170</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44710</v>
+        <v>46276</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.9</v>
+        <v>11.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8965,14 +8965,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46276</v>
+        <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11.6</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>44746</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44943</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 55111-2025</t>
+          <t>A 22268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45968</v>
+        <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>16.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1206,148 +1206,148 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Havstulpanlav
+Stubbspretmossa
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 55111-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stor revmossa
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 22268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44712</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Havstulpanlav
-Stubbspretmossa
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44895</v>
+        <v>44623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1953,46 +1953,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44943</v>
+        <v>45057</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2055,42 +2055,42 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         <v>45092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45057</v>
+        <v>44895</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2272,42 +2272,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>44943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2370,42 +2370,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 468-2022</t>
+          <t>A 22240-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3042,14 +3042,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44566</v>
+        <v>44712</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22240-2022</t>
+          <t>A 15138-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44712</v>
+        <v>44658</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 15138-2022</t>
+          <t>A 468-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3188,14 +3188,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44658</v>
+        <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44746</v>
+        <v>44700</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45345</v>
+        <v>44809</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45217</v>
+        <v>45170</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45350</v>
+        <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3772,14 +3772,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45216</v>
+        <v>45300</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45216</v>
+        <v>44746</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45412</v>
+        <v>45350</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3991,14 +3991,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44828</v>
+        <v>45441</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45329</v>
+        <v>45217</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45887</v>
+        <v>45392</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45887</v>
+        <v>44959</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45897</v>
+        <v>45216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45805</v>
+        <v>45216</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4429,14 +4429,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45812</v>
+        <v>44746</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46034</v>
+        <v>44710</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45476</v>
+        <v>45548</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45476</v>
+        <v>44828</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46036</v>
+        <v>45565</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4740,8 +4740,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4789,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4794,14 +4799,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45548</v>
+        <v>45386</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4819,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4862,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4876,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45922</v>
+        <v>45476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4892,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4935,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4944,10 +4949,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4965,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5008,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5017,10 +5022,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45919</v>
+        <v>45145</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5038,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5081,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5090,10 +5095,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>45587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5111,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5149,7 +5154,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5168,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45835</v>
+        <v>45350</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5179,7 +5184,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5227,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5236,10 +5241,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45835</v>
+        <v>45805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5257,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5300,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5309,10 +5314,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45145</v>
+        <v>45345</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5330,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5373,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5382,10 +5387,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45929</v>
+        <v>45812</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5403,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5446,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5460,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45931</v>
+        <v>45412</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5476,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5514,7 +5519,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5528,10 +5533,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44895</v>
+        <v>45055</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5549,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5592,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5606,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44517</v>
+        <v>45835</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5622,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5665,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5679,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44517</v>
+        <v>45835</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5695,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5738,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5752,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44517</v>
+        <v>45028</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5762,8 +5767,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5816,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5830,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44805</v>
+        <v>44746</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5846,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5889,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5893,10 +5903,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44895</v>
+        <v>45887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5919,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5969,7 +5979,7 @@
         <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6025,7 +6035,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6039,10 +6049,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44943</v>
+        <v>45887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6065,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6108,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6122,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44895</v>
+        <v>45588</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6138,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6181,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6181,14 +6191,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44895</v>
+        <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6244,7 +6254,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6254,14 +6264,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44895</v>
+        <v>45919</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6284,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6327,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6341,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45565</v>
+        <v>45922</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6346,13 +6356,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6395,7 +6400,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6405,14 +6410,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45726</v>
+        <v>45922</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6425,7 +6430,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6468,7 +6473,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6482,10 +6487,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45588</v>
+        <v>45922</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6498,7 +6503,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6558,7 +6563,7 @@
         <v>45971</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6614,7 +6619,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6624,14 +6629,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45028</v>
+        <v>45929</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6643,13 +6648,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6702,14 +6702,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45386</v>
+        <v>45931</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45982</v>
+        <v>44517</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46002</v>
+        <v>44895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46002</v>
+        <v>44895</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6984,7 +6984,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6998,10 +6998,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46008</v>
+        <v>44895</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46008</v>
+        <v>44805</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7130,7 +7130,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44809</v>
+        <v>44943</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7213,14 +7213,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44704</v>
+        <v>44517</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7276,7 +7276,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46132</v>
+        <v>44517</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7349,7 +7349,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7363,10 +7363,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45392</v>
+        <v>44895</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7422,7 +7422,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45587</v>
+        <v>44895</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7495,7 +7495,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45723</v>
+        <v>45982</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44712</v>
+        <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>23.3</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7641,7 +7641,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45917</v>
+        <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45350</v>
+        <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7874,10 +7874,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45817</v>
+        <v>45329</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7933,7 +7933,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45589</v>
+        <v>46034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8006,7 +8006,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8020,10 +8020,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45216</v>
+        <v>46036</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8079,7 +8079,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45055</v>
+        <v>45726</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8152,7 +8152,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8162,14 +8162,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45817</v>
+        <v>44704</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8239,10 +8239,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45216</v>
+        <v>46132</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8298,7 +8298,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8312,10 +8312,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44710</v>
+        <v>44712</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.9</v>
+        <v>23.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8371,7 +8371,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44746</v>
+        <v>45917</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8444,7 +8444,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8454,14 +8454,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45441</v>
+        <v>45817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8517,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46206</v>
+        <v>45834</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44700</v>
+        <v>45589</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44746</v>
+        <v>45723</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8746,14 +8746,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44959</v>
+        <v>45216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45170</v>
+        <v>45817</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46276</v>
+        <v>46206</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>11.6</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8965,14 +8965,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45300</v>
+        <v>46276</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>44746</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44943</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 22268-2022</t>
+          <t>A 55111-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44712</v>
+        <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>16.6</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1206,148 +1206,148 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Stor revmossa
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 22268-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Havstulpanlav
 Stubbspretmossa
 Mattlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 55111-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Stor revmossa
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44623</v>
+        <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1953,46 +1953,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45057</v>
+        <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2055,42 +2055,42 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         <v>45092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44895</v>
+        <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2272,42 +2272,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44943</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2370,42 +2370,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22240-2022</t>
+          <t>A 468-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3042,14 +3042,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44712</v>
+        <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15138-2022</t>
+          <t>A 22240-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44658</v>
+        <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 468-2022</t>
+          <t>A 15138-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3188,14 +3188,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44566</v>
+        <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44700</v>
+        <v>44746</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44809</v>
+        <v>45350</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45170</v>
+        <v>45412</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45216</v>
+        <v>45345</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3772,14 +3772,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45300</v>
+        <v>45216</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44746</v>
+        <v>45216</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45350</v>
+        <v>45217</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3991,14 +3991,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45441</v>
+        <v>44828</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45217</v>
+        <v>45329</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45392</v>
+        <v>46034</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44959</v>
+        <v>46036</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4429,14 +4429,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44746</v>
+        <v>45897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44710</v>
+        <v>45726</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.9</v>
+        <v>0.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45548</v>
+        <v>45922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44828</v>
+        <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4721,14 +4721,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45565</v>
+        <v>45919</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4740,13 +4740,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4789,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4799,14 +4794,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45386</v>
+        <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4819,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4862,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4879,7 +4874,7 @@
         <v>45476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4892,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4935,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4949,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45476</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4965,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5008,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5022,10 +5017,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45145</v>
+        <v>45929</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5038,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5081,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5095,10 +5090,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45587</v>
+        <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5111,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5154,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5168,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45350</v>
+        <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5184,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5244,7 +5239,7 @@
         <v>45805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5300,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5310,14 +5305,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45345</v>
+        <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5330,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5373,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5383,14 +5378,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45812</v>
+        <v>44517</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5403,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5446,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5460,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45412</v>
+        <v>45548</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5476,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5519,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5533,10 +5528,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45055</v>
+        <v>44517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5549,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5592,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5606,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45835</v>
+        <v>44805</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5622,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5665,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5679,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45835</v>
+        <v>44895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5695,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5738,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5752,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45028</v>
+        <v>44970</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5767,13 +5762,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5816,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5830,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44746</v>
+        <v>44943</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5846,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5889,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5903,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45887</v>
+        <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5919,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5962,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5976,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44970</v>
+        <v>44895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5992,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6035,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6049,10 +6039,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45887</v>
+        <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6065,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6108,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6118,14 +6108,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45588</v>
+        <v>45145</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6138,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6181,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6195,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45897</v>
+        <v>45812</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6211,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6254,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6264,14 +6254,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45919</v>
+        <v>45971</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6284,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6327,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6341,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45922</v>
+        <v>45565</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6356,8 +6346,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6400,7 +6395,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6410,14 +6405,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45922</v>
+        <v>44704</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6430,7 +6425,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6473,7 +6468,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6487,10 +6482,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45922</v>
+        <v>46132</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6503,7 +6498,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6546,7 +6541,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6560,10 +6555,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6576,7 +6571,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6619,7 +6614,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6629,14 +6624,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45929</v>
+        <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6648,8 +6643,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>8.699999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6702,14 +6702,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45931</v>
+        <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44517</v>
+        <v>45723</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44895</v>
+        <v>44712</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>23.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44895</v>
+        <v>46002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6984,7 +6984,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6998,10 +6998,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44895</v>
+        <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44805</v>
+        <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7130,7 +7130,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44943</v>
+        <v>45834</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44517</v>
+        <v>46008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7276,7 +7276,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44517</v>
+        <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7349,7 +7349,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7363,10 +7363,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44895</v>
+        <v>45835</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7422,7 +7422,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44895</v>
+        <v>45835</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7495,7 +7495,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45982</v>
+        <v>45817</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46002</v>
+        <v>45589</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7641,7 +7641,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46002</v>
+        <v>45588</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46008</v>
+        <v>44809</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7787,7 +7787,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7860,7 +7860,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7874,10 +7874,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45329</v>
+        <v>45392</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7933,7 +7933,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46034</v>
+        <v>45817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8006,7 +8006,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8020,10 +8020,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46036</v>
+        <v>45587</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8079,7 +8079,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45726</v>
+        <v>45350</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8152,7 +8152,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8162,14 +8162,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44704</v>
+        <v>45055</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8239,10 +8239,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46132</v>
+        <v>45216</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8298,7 +8298,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8312,10 +8312,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44712</v>
+        <v>46206</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>23.3</v>
+        <v>3.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8371,7 +8371,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45917</v>
+        <v>44710</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8444,7 +8444,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8458,10 +8458,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45817</v>
+        <v>44746</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8517,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45834</v>
+        <v>46276</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>11.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8600,14 +8600,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45589</v>
+        <v>45441</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45723</v>
+        <v>44700</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45216</v>
+        <v>44746</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45817</v>
+        <v>46245</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8892,14 +8892,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46206</v>
+        <v>44959</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8969,10 +8969,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46276</v>
+        <v>46290</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11.6</v>
+        <v>7.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46245</v>
+        <v>45170</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46290</v>
+        <v>45300</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.3</v>
+        <v>0.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,257 +1104,36 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45092</v>
+        <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2163,39 +2163,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2373,39 +2373,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44746</v>
+        <v>45217</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45350</v>
+        <v>45548</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45412</v>
+        <v>46002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45345</v>
+        <v>45887</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45216</v>
+        <v>46002</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45216</v>
+        <v>46008</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45217</v>
+        <v>46008</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44828</v>
+        <v>45887</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45329</v>
+        <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46034</v>
+        <v>45329</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46036</v>
+        <v>45897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45887</v>
+        <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45887</v>
+        <v>46034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4429,14 +4429,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45897</v>
+        <v>46036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45726</v>
+        <v>45919</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45922</v>
+        <v>45805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4655,7 +4655,7 @@
         <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4721,14 +4721,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45476</v>
+        <v>45055</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45476</v>
+        <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45929</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45929</v>
+        <v>45726</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.699999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45805</v>
+        <v>44895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45548</v>
+        <v>44805</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5514,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44517</v>
+        <v>44943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44805</v>
+        <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44970</v>
+        <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44943</v>
+        <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44895</v>
+        <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44895</v>
+        <v>44746</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6035,14 +6035,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44895</v>
+        <v>45812</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6108,14 +6108,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45145</v>
+        <v>44809</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6181,14 +6181,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45812</v>
+        <v>45971</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45971</v>
+        <v>45216</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45565</v>
+        <v>44746</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6346,13 +6346,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6395,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6405,14 +6400,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44704</v>
+        <v>45350</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6425,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6468,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46132</v>
+        <v>45982</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6498,7 +6493,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6541,7 +6536,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6555,10 +6550,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45982</v>
+        <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6571,7 +6566,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45028</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6643,13 +6638,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6692,7 +6682,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6702,14 +6692,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45386</v>
+        <v>44704</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6765,7 +6755,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6779,10 +6769,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45723</v>
+        <v>46132</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6795,7 +6785,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6838,7 +6828,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6852,10 +6842,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44712</v>
+        <v>44828</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6868,7 +6858,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>23.3</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6911,7 +6901,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6925,10 +6915,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46002</v>
+        <v>45835</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6941,7 +6931,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6984,7 +6974,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6998,10 +6988,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45917</v>
+        <v>45835</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7014,7 +7004,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7057,7 +7047,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7071,10 +7061,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46002</v>
+        <v>44712</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7087,7 +7077,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>23.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7130,7 +7120,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7144,10 +7134,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45834</v>
+        <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7160,7 +7150,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7203,7 +7193,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7217,10 +7207,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46008</v>
+        <v>45817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7233,7 +7223,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7276,7 +7266,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7290,10 +7280,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46008</v>
+        <v>45834</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7349,7 +7339,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7363,10 +7353,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45835</v>
+        <v>45589</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7379,7 +7369,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7422,7 +7412,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7436,10 +7426,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45835</v>
+        <v>45723</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7452,7 +7442,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7495,7 +7485,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7509,10 +7499,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45817</v>
+        <v>45587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7525,7 +7515,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7568,7 +7558,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7578,14 +7568,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45589</v>
+        <v>45345</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7598,7 +7588,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7641,7 +7631,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7655,10 +7645,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45588</v>
+        <v>45412</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7671,7 +7661,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7714,7 +7704,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7728,10 +7718,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44809</v>
+        <v>45216</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7744,7 +7734,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7787,7 +7777,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7801,10 +7791,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45216</v>
+        <v>45817</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7817,7 +7807,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7860,7 +7850,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7874,10 +7864,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45392</v>
+        <v>45588</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7890,7 +7880,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7933,7 +7923,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7947,10 +7937,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45817</v>
+        <v>44700</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7963,7 +7953,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8006,7 +7996,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8020,10 +8010,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45587</v>
+        <v>45170</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8036,7 +8026,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8079,7 +8069,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8089,14 +8079,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45350</v>
+        <v>45441</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8109,7 +8099,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8152,7 +8142,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8166,10 +8156,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45055</v>
+        <v>45392</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8182,7 +8172,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8225,7 +8215,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8239,10 +8229,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45216</v>
+        <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8255,7 +8245,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8298,7 +8288,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8308,14 +8298,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46206</v>
+        <v>44959</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8328,7 +8318,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8371,7 +8361,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8385,10 +8375,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44710</v>
+        <v>45565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8400,8 +8390,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8444,7 +8439,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8458,10 +8453,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44746</v>
+        <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8474,7 +8469,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.4</v>
+        <v>11.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8517,7 +8512,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8531,10 +8526,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46276</v>
+        <v>45476</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8547,7 +8542,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>11.6</v>
+        <v>7.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8585,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8600,14 +8595,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45441</v>
+        <v>45476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8615,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8658,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8677,10 +8672,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44700</v>
+        <v>45350</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8688,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8731,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8750,10 +8745,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44746</v>
+        <v>46245</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8761,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8804,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8818,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46245</v>
+        <v>46290</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8834,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8877,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8892,14 +8887,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44959</v>
+        <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8911,8 +8906,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8965,14 +8965,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46290</v>
+        <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7.3</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45170</v>
+        <v>44746</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45300</v>
+        <v>44710</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45217</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45548</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>46002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45887</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>46002</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46008</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>46008</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45887</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45329</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>46034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45919</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45055</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45929</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45726</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>44895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>44805</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>44943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44746</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45812</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44809</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45971</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45216</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>44746</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>45350</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45982</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44704</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>46132</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>44828</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45835</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45835</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44712</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45834</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45589</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45723</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>45345</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>45412</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45216</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45817</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>45588</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>44700</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45170</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45441</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45392</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44959</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>45476</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45350</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46245</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>46290</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44746</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44710</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45217</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45548</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>46002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45887</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>46002</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46008</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>46008</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45887</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45329</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>46034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45919</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45055</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45929</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45726</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>44895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>44805</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>44943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44746</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45812</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44809</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45971</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45216</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>44746</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>45350</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45982</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44704</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>46132</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>44828</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45835</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45835</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44712</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45834</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45589</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45723</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>45345</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>45412</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45216</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45817</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>45588</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>44700</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45170</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45441</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45392</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44959</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>45476</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45350</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>46245</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>46290</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44746</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44710</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,144 +1108,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44895</v>
+        <v>45092</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1957,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44943</v>
+        <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2055,49 +2055,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44623</v>
+        <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2160,42 +2160,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45092</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2373,39 +2373,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45217</v>
+        <v>44746</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45548</v>
+        <v>45350</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46002</v>
+        <v>45412</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45887</v>
+        <v>45345</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46002</v>
+        <v>45217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45887</v>
+        <v>44828</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45386</v>
+        <v>45805</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45329</v>
+        <v>45476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45897</v>
+        <v>45476</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45145</v>
+        <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46034</v>
+        <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46036</v>
+        <v>45887</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45919</v>
+        <v>45548</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45805</v>
+        <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45922</v>
+        <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45922</v>
+        <v>45835</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4794,14 +4794,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45055</v>
+        <v>45145</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4874,7 +4874,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45929</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45726</v>
+        <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45931</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44517</v>
+        <v>45565</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5178,8 +5178,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5227,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5232,14 +5237,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44895</v>
+        <v>45726</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5257,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5300,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5305,14 +5310,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44895</v>
+        <v>45929</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5330,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5373,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5382,10 +5387,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44895</v>
+        <v>45931</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5441,7 +5446,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5460,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44805</v>
+        <v>44895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5476,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5514,7 +5519,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5528,10 +5533,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44943</v>
+        <v>44517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5549,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5592,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5604,7 +5609,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5622,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5665,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5677,7 +5682,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5695,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5738,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5752,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44895</v>
+        <v>44805</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5768,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5811,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5823,7 +5828,7 @@
         <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5841,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5896,7 +5901,7 @@
         <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5952,7 +5957,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5966,10 +5971,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44746</v>
+        <v>44943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5987,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6025,7 +6030,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6035,14 +6040,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45812</v>
+        <v>45588</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6060,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6103,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44809</v>
+        <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6133,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6176,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6185,10 +6190,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45971</v>
+        <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6206,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6249,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6258,10 +6263,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45216</v>
+        <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6279,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6322,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6336,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44746</v>
+        <v>45028</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6346,8 +6351,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6390,7 +6400,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6400,14 +6410,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45350</v>
+        <v>45386</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6420,7 +6430,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6463,7 +6473,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6477,10 +6487,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45982</v>
+        <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6493,7 +6503,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6536,7 +6546,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6550,10 +6560,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45216</v>
+        <v>45982</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6566,7 +6576,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6609,7 +6619,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6619,14 +6629,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>44704</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6639,7 +6649,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6682,7 +6692,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6692,14 +6702,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44704</v>
+        <v>46132</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6712,7 +6722,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6755,7 +6765,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6769,10 +6779,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46132</v>
+        <v>44809</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6785,7 +6795,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6828,7 +6838,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6842,10 +6852,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44828</v>
+        <v>46002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6858,7 +6868,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6901,7 +6911,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6915,10 +6925,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45835</v>
+        <v>46002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6931,7 +6941,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6974,7 +6984,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6988,10 +6998,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45835</v>
+        <v>46008</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7004,7 +7014,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7047,7 +7057,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7061,10 +7071,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44712</v>
+        <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7077,7 +7087,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>23.3</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7120,7 +7130,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45917</v>
+        <v>45329</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7150,7 +7160,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>6.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7193,7 +7203,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7207,10 +7217,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45817</v>
+        <v>45392</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7223,7 +7233,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7266,7 +7276,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7280,10 +7290,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45834</v>
+        <v>45723</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7296,7 +7306,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7339,7 +7349,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7353,10 +7363,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45589</v>
+        <v>44712</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7369,7 +7379,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>23.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7412,7 +7422,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7426,10 +7436,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45723</v>
+        <v>45587</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7442,7 +7452,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7485,7 +7495,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7499,10 +7509,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45587</v>
+        <v>46034</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7515,7 +7525,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7558,7 +7568,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7568,14 +7578,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45345</v>
+        <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7588,7 +7598,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7631,7 +7641,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7645,10 +7655,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45412</v>
+        <v>46036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7661,7 +7671,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7704,7 +7714,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7718,10 +7728,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45216</v>
+        <v>45834</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7734,7 +7744,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7777,7 +7787,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7791,10 +7801,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45817</v>
+        <v>45350</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7807,7 +7817,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7850,7 +7860,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7864,10 +7874,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45588</v>
+        <v>45817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7880,7 +7890,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7923,7 +7933,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7937,10 +7947,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44700</v>
+        <v>45589</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7953,7 +7963,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7996,7 +8006,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8010,10 +8020,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45170</v>
+        <v>45216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8026,7 +8036,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8069,7 +8079,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8079,14 +8089,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45441</v>
+        <v>45817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8099,7 +8109,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8142,7 +8152,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8156,10 +8166,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45392</v>
+        <v>45055</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8172,7 +8182,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8215,7 +8225,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8229,10 +8239,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46206</v>
+        <v>45216</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8245,7 +8255,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8288,7 +8298,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8298,14 +8308,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44959</v>
+        <v>44710</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8318,7 +8328,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8361,7 +8371,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8375,10 +8385,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45565</v>
+        <v>44746</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8390,13 +8400,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>7.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8439,7 +8444,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8453,10 +8458,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46276</v>
+        <v>46206</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8469,7 +8474,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>11.6</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8512,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8522,14 +8527,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45476</v>
+        <v>45441</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8542,7 +8547,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8585,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8599,10 +8604,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45476</v>
+        <v>44700</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8615,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8658,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8672,10 +8677,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45350</v>
+        <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8688,7 +8693,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8731,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8745,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46245</v>
+        <v>46276</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8761,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>11.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8804,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8814,14 +8819,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46290</v>
+        <v>44959</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8834,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8877,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8891,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45028</v>
+        <v>45170</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8906,13 +8911,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
         <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44746</v>
+        <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44710</v>
+        <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,257 +1104,36 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45092</v>
+        <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1957,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2055,49 +2055,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44943</v>
+        <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2160,42 +2160,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2373,39 +2373,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44746</v>
+        <v>45217</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45350</v>
+        <v>45548</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3626,14 +3626,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45412</v>
+        <v>45386</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45345</v>
+        <v>45145</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45217</v>
+        <v>45887</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45216</v>
+        <v>45055</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45216</v>
+        <v>45805</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44828</v>
+        <v>46034</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45805</v>
+        <v>46036</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45476</v>
+        <v>45887</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.2</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45476</v>
+        <v>44746</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4356,14 +4356,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4429,14 +4429,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45887</v>
+        <v>45726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45548</v>
+        <v>45919</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45897</v>
+        <v>45922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45835</v>
+        <v>45922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45835</v>
+        <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4794,14 +4794,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45145</v>
+        <v>44809</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45922</v>
+        <v>45929</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45931</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45919</v>
+        <v>44517</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45565</v>
+        <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5178,13 +5178,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5227,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5237,14 +5232,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45726</v>
+        <v>44895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5257,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5300,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5310,14 +5305,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45929</v>
+        <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5330,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5373,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5387,10 +5382,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45931</v>
+        <v>44943</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5403,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5446,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5460,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5476,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5536,7 +5531,7 @@
         <v>44517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5592,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5606,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5622,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5665,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5679,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5695,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5738,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5752,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44805</v>
+        <v>44970</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5768,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5811,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5825,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44895</v>
+        <v>45216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5841,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5884,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5898,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44970</v>
+        <v>45835</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5914,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5957,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5971,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44943</v>
+        <v>44746</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5987,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6030,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6044,10 +6039,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45588</v>
+        <v>45835</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6060,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6103,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6117,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44895</v>
+        <v>45350</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6133,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6176,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6186,14 +6181,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44895</v>
+        <v>44704</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6206,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6249,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6263,10 +6258,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44895</v>
+        <v>45216</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6279,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6322,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6336,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45028</v>
+        <v>45216</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6351,13 +6346,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6400,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6410,14 +6400,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45386</v>
+        <v>45588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6430,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6473,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6487,10 +6477,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45971</v>
+        <v>46132</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6503,7 +6493,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6546,7 +6536,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6560,10 +6550,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45982</v>
+        <v>45971</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6576,7 +6566,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6619,7 +6609,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6629,14 +6619,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44704</v>
+        <v>44828</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6649,7 +6639,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6692,7 +6682,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6706,10 +6696,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46132</v>
+        <v>44712</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6722,7 +6712,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>23.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6765,7 +6755,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6779,10 +6769,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44809</v>
+        <v>45982</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6795,7 +6785,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6838,7 +6828,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6852,10 +6842,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46002</v>
+        <v>45917</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6868,7 +6858,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6911,7 +6901,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6925,10 +6915,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46002</v>
+        <v>45817</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6984,7 +6974,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6998,10 +6988,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46008</v>
+        <v>45834</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7014,7 +7004,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7057,7 +7047,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7071,10 +7061,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46008</v>
+        <v>45589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7087,7 +7077,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7130,7 +7120,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7144,10 +7134,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45329</v>
+        <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7160,7 +7150,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7203,7 +7193,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7217,10 +7207,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45392</v>
+        <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7233,7 +7223,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7293,7 +7283,7 @@
         <v>45723</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7349,7 +7339,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7363,10 +7353,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44712</v>
+        <v>46008</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7379,7 +7369,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>23.3</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7422,7 +7412,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7436,10 +7426,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45587</v>
+        <v>46008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7452,7 +7442,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7495,7 +7485,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7509,10 +7499,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46034</v>
+        <v>45329</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7525,7 +7515,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7568,7 +7558,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7582,10 +7572,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45917</v>
+        <v>45216</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7598,7 +7588,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7641,7 +7631,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7655,10 +7645,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46036</v>
+        <v>45817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7671,7 +7661,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7714,7 +7704,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7728,10 +7718,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45834</v>
+        <v>45587</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7744,7 +7734,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7787,7 +7777,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7797,14 +7787,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45350</v>
+        <v>45345</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7817,7 +7807,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7860,7 +7850,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7874,10 +7864,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45817</v>
+        <v>45412</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7890,7 +7880,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7933,7 +7923,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7947,10 +7937,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45589</v>
+        <v>46206</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7963,7 +7953,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8006,7 +7996,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8020,10 +8010,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45216</v>
+        <v>44700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8036,7 +8026,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8079,7 +8069,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8093,10 +8083,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45817</v>
+        <v>45170</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8109,7 +8099,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8152,7 +8142,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8162,14 +8152,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45055</v>
+        <v>45441</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8182,7 +8172,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8225,7 +8215,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8239,10 +8229,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45216</v>
+        <v>45392</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8255,7 +8245,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8298,7 +8288,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8308,14 +8298,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44710</v>
+        <v>44959</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8328,7 +8318,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8371,7 +8361,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8385,10 +8375,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44746</v>
+        <v>46276</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8401,7 +8391,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.4</v>
+        <v>11.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8444,7 +8434,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8458,10 +8448,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46206</v>
+        <v>45565</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8473,8 +8463,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8517,7 +8512,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8527,14 +8522,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45441</v>
+        <v>46245</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8547,7 +8542,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8585,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8604,10 +8599,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44700</v>
+        <v>46290</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8615,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>7.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8658,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8677,10 +8672,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44746</v>
+        <v>45476</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8688,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8731,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8750,10 +8745,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46276</v>
+        <v>45476</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8761,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>11.6</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8804,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8819,14 +8814,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44959</v>
+        <v>45350</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8834,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8877,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8891,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45170</v>
+        <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8911,8 +8906,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
         <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46245</v>
+        <v>44746</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46290</v>
+        <v>44710</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,144 +1108,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44895</v>
+        <v>45057</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1957,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44943</v>
+        <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2055,49 +2055,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44623</v>
+        <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2160,49 +2160,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45057</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2268,39 +2268,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 69614-2021</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44532</v>
+        <v>45350</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 69628-2021</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44532</v>
+        <v>45412</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 69614-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45217</v>
+        <v>44532</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 69628-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45548</v>
+        <v>44532</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3626,14 +3626,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45386</v>
+        <v>44746</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45145</v>
+        <v>45345</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45887</v>
+        <v>45588</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45055</v>
+        <v>45217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45805</v>
+        <v>44809</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46034</v>
+        <v>45216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46036</v>
+        <v>45216</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4144,7 +4144,7 @@
         <v>45887</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44746</v>
+        <v>45887</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.4</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45812</v>
+        <v>44828</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>45897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4429,14 +4429,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45726</v>
+        <v>45392</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45919</v>
+        <v>45805</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45922</v>
+        <v>45587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4648,14 +4648,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45922</v>
+        <v>45812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4728,7 +4728,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44809</v>
+        <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45929</v>
+        <v>45919</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.699999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45931</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44517</v>
+        <v>45350</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5086,14 +5086,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44895</v>
+        <v>45929</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44895</v>
+        <v>45931</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5239,7 +5239,7 @@
         <v>44895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44805</v>
+        <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44943</v>
+        <v>44517</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>44517</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44517</v>
+        <v>44805</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5604,7 +5604,7 @@
         <v>44895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44895</v>
+        <v>44970</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44970</v>
+        <v>44943</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45216</v>
+        <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45835</v>
+        <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44746</v>
+        <v>44895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6042,7 +6042,7 @@
         <v>45835</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45350</v>
+        <v>45835</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6181,14 +6181,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44704</v>
+        <v>45476</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45216</v>
+        <v>45476</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45216</v>
+        <v>45548</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6400,14 +6400,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45588</v>
+        <v>45145</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46132</v>
+        <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45971</v>
+        <v>44712</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.3</v>
+        <v>23.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6609,7 +6609,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44828</v>
+        <v>45917</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44712</v>
+        <v>45055</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>23.3</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45982</v>
+        <v>45834</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45917</v>
+        <v>45982</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6918,7 +6918,7 @@
         <v>45817</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45834</v>
+        <v>45589</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45589</v>
+        <v>45216</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46002</v>
+        <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7149,8 +7149,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7193,7 +7198,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7207,10 +7212,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46002</v>
+        <v>45216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7223,7 +7228,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7266,7 +7271,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7280,10 +7285,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45723</v>
+        <v>45817</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7296,7 +7301,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7339,7 +7344,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7353,10 +7358,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7369,7 +7374,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7412,7 +7417,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7426,10 +7431,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7442,7 +7447,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7485,7 +7490,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7499,10 +7504,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45329</v>
+        <v>45028</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7514,8 +7519,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7558,7 +7568,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7568,14 +7578,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45216</v>
+        <v>45386</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7588,7 +7598,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7631,7 +7641,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7645,10 +7655,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45817</v>
+        <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7661,7 +7671,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7704,7 +7714,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7718,10 +7728,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45587</v>
+        <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7734,7 +7744,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7777,7 +7787,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7787,14 +7797,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45345</v>
+        <v>44710</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7807,7 +7817,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7850,7 +7860,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7864,10 +7874,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45412</v>
+        <v>44746</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7880,7 +7890,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>7.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7923,7 +7933,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7937,10 +7947,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46206</v>
+        <v>45329</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7953,7 +7963,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7996,7 +8006,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8010,10 +8020,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44700</v>
+        <v>46034</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8026,7 +8036,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8069,7 +8079,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8083,10 +8093,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45170</v>
+        <v>46036</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8099,7 +8109,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8142,7 +8152,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8152,14 +8162,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45441</v>
+        <v>45726</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8172,7 +8182,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8215,7 +8225,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8225,14 +8235,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45392</v>
+        <v>45441</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8288,7 +8298,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8298,14 +8308,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44959</v>
+        <v>44700</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8318,7 +8328,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8361,7 +8371,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8375,10 +8385,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46276</v>
+        <v>44746</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8391,7 +8401,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>11.6</v>
+        <v>5.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8434,7 +8444,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8448,10 +8458,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45565</v>
+        <v>46206</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8463,13 +8473,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8512,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8522,14 +8527,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46245</v>
+        <v>44959</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8542,7 +8547,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8585,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8595,14 +8600,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46290</v>
+        <v>44704</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8615,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8658,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8672,10 +8677,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45476</v>
+        <v>46132</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8688,7 +8693,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8731,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8745,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45476</v>
+        <v>45170</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8761,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8804,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8814,14 +8819,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45350</v>
+        <v>45300</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8834,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8877,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8891,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45028</v>
+        <v>45723</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8906,13 +8911,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8965,14 +8965,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45300</v>
+        <v>46276</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44746</v>
+        <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44710</v>
+        <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,264 +1104,43 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 55111-2025</t>
+          <t>A 22268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45968</v>
+        <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>16.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1206,148 +1206,148 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Havstulpanlav
+Stubbspretmossa
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 55111-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stor revmossa
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 22268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44712</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Havstulpanlav
-Stubbspretmossa
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45057</v>
+        <v>44623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1953,39 +1953,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
         <v>44895</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44943</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44623</v>
+        <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2268,39 +2268,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>45092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 69614-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45350</v>
+        <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 69628-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45412</v>
+        <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 69614-2021</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44532</v>
+        <v>45217</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 69628-2021</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44532</v>
+        <v>45548</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3626,14 +3626,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44746</v>
+        <v>45386</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45345</v>
+        <v>45145</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45588</v>
+        <v>45055</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45217</v>
+        <v>44746</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44809</v>
+        <v>45835</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45216</v>
+        <v>44809</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45887</v>
+        <v>45216</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44828</v>
+        <v>44746</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4356,14 +4356,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45897</v>
+        <v>45350</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45392</v>
+        <v>45588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45805</v>
+        <v>45216</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45587</v>
+        <v>45216</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45812</v>
+        <v>45919</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4801,7 +4801,7 @@
         <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>45887</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45350</v>
+        <v>45929</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5086,14 +5086,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45929</v>
+        <v>44828</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>45931</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44895</v>
+        <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44517</v>
+        <v>44895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>44805</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44970</v>
+        <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44943</v>
+        <v>44517</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5823,7 +5823,7 @@
         <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5896,7 +5896,7 @@
         <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44895</v>
+        <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6035,14 +6035,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45835</v>
+        <v>44704</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45835</v>
+        <v>45971</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45476</v>
+        <v>45587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45476</v>
+        <v>46132</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45548</v>
+        <v>45982</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45145</v>
+        <v>45345</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45971</v>
+        <v>45412</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>44712</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45917</v>
+        <v>46002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45055</v>
+        <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45982</v>
+        <v>46008</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6901,7 +6901,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45817</v>
+        <v>45329</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45589</v>
+        <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45216</v>
+        <v>45817</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45565</v>
+        <v>45834</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7149,13 +7149,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7198,7 +7193,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7212,10 +7207,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45216</v>
+        <v>45589</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7228,7 +7223,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7271,7 +7266,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7285,10 +7280,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45817</v>
+        <v>46034</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7301,7 +7296,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7344,7 +7339,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7358,10 +7353,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46002</v>
+        <v>46036</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7374,7 +7369,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7417,7 +7412,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7431,10 +7426,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46002</v>
+        <v>44700</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7447,7 +7442,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7490,7 +7485,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7504,10 +7499,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45028</v>
+        <v>45723</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7519,13 +7514,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7568,7 +7558,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7578,14 +7568,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45386</v>
+        <v>45170</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7641,7 +7631,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7651,14 +7641,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46008</v>
+        <v>45726</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7671,7 +7661,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7714,7 +7704,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7724,14 +7714,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46008</v>
+        <v>45441</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7744,7 +7734,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7787,7 +7777,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7801,10 +7791,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44710</v>
+        <v>45392</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7817,7 +7807,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7860,7 +7850,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7874,10 +7864,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44746</v>
+        <v>45216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7890,7 +7880,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7933,7 +7923,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7943,14 +7933,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45329</v>
+        <v>44959</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7963,7 +7953,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8006,7 +7996,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8020,10 +8010,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46034</v>
+        <v>45817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8036,7 +8026,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8079,7 +8069,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8093,10 +8083,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46036</v>
+        <v>45565</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8108,8 +8098,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8152,7 +8147,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8162,14 +8157,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45726</v>
+        <v>45476</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8182,7 +8177,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.1</v>
+        <v>7.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8225,7 +8220,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8235,14 +8230,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45441</v>
+        <v>45476</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8255,7 +8250,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8298,7 +8293,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8312,10 +8307,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44700</v>
+        <v>45350</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8328,7 +8323,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8371,7 +8366,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8385,10 +8380,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44746</v>
+        <v>45028</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8400,8 +8395,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8461,7 +8461,7 @@
         <v>46206</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44959</v>
+        <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8600,14 +8600,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44704</v>
+        <v>44746</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46132</v>
+        <v>44710</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45170</v>
+        <v>46276</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>11.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8819,14 +8819,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45300</v>
+        <v>46245</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45723</v>
+        <v>45805</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8969,10 +8969,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46276</v>
+        <v>46290</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11.6</v>
+        <v>7.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9038,14 +9038,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46245</v>
+        <v>45812</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46290</v>
+        <v>45835</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,144 +1108,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45968</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 57154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44623</v>
+        <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1953,46 +1953,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57154-2022</t>
+          <t>A 2438-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44895</v>
+        <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2055,49 +2055,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 57154-2022 artfynd.xlsx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 57154-2022 karta.png", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 57154-2022 georefererad karta.tif", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 57154-2022 FSC-klagomål.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 57154-2022 FSC-klagomål mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 57154-2022 tillsynsbegäran.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 57154-2022 tillsynsbegäran mail.docx", "A 57154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2438-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44943</v>
+        <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2160,49 +2160,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2438-2023 artfynd.xlsx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2438-2023 karta.png", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2438-2023 georefererad karta.tif", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2438-2023 FSC-klagomål.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2438-2023 FSC-klagomål mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2438-2023 tillsynsbegäran.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2438-2023 tillsynsbegäran mail.docx", "A 2438-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45057</v>
+        <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2272,42 +2272,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45092</v>
+        <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2377,35 +2377,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 468-2022</t>
+          <t>A 29101-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3042,14 +3042,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44566</v>
+        <v>44750</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22240-2022</t>
+          <t>A 468-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3115,14 +3115,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44712</v>
+        <v>44566</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 15138-2022</t>
+          <t>A 69614-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44658</v>
+        <v>44532</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29101-2022</t>
+          <t>A 69628-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44750</v>
+        <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 69614-2021</t>
+          <t>A 22240-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44532</v>
+        <v>44712</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 69628-2021</t>
+          <t>A 15138-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44532</v>
+        <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45217</v>
+        <v>44809</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45548</v>
+        <v>45350</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3626,14 +3626,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45386</v>
+        <v>45216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45145</v>
+        <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45055</v>
+        <v>45412</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3852,7 +3852,7 @@
         <v>44746</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45835</v>
+        <v>45170</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44809</v>
+        <v>44828</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45887</v>
+        <v>45392</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4137,14 +4137,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45216</v>
+        <v>45345</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45897</v>
+        <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44746</v>
+        <v>45300</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45350</v>
+        <v>45588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45588</v>
+        <v>45587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4648,14 +4648,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45919</v>
+        <v>45350</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4721,14 +4721,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45922</v>
+        <v>45897</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45922</v>
+        <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45922</v>
+        <v>45476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45887</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45929</v>
+        <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5086,14 +5086,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44828</v>
+        <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45931</v>
+        <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44517</v>
+        <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44895</v>
+        <v>45929</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5378,14 +5378,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44895</v>
+        <v>45145</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44895</v>
+        <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44805</v>
+        <v>44895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44943</v>
+        <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5677,7 +5677,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5750,7 +5750,7 @@
         <v>44517</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44895</v>
+        <v>44805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5896,7 +5896,7 @@
         <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5969,7 +5969,7 @@
         <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6035,14 +6035,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44704</v>
+        <v>44943</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45971</v>
+        <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45587</v>
+        <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46132</v>
+        <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45982</v>
+        <v>45805</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6400,14 +6400,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45345</v>
+        <v>45055</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6473,14 +6473,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45412</v>
+        <v>45812</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44712</v>
+        <v>45565</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6565,8 +6565,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>23.3</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6609,7 +6614,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6623,10 +6628,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46002</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6639,7 +6644,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6682,7 +6687,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6696,10 +6701,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46002</v>
+        <v>45028</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6711,8 +6716,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6755,7 +6765,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6769,10 +6779,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46008</v>
+        <v>45835</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6785,7 +6795,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6828,7 +6838,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6842,10 +6852,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46008</v>
+        <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6858,7 +6868,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6901,7 +6911,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6911,14 +6921,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45329</v>
+        <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6931,7 +6941,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6974,7 +6984,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6988,10 +6998,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45917</v>
+        <v>45971</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7004,7 +7014,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7047,7 +7057,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7061,10 +7071,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45817</v>
+        <v>44710</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7077,7 +7087,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7120,7 +7130,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45834</v>
+        <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7150,7 +7160,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7193,7 +7203,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7207,10 +7217,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45589</v>
+        <v>45982</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7223,7 +7233,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7266,7 +7276,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7276,14 +7286,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46034</v>
+        <v>44704</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7296,7 +7306,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7339,7 +7349,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7349,14 +7359,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46036</v>
+        <v>45441</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7369,7 +7379,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7412,7 +7422,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7426,10 +7436,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44700</v>
+        <v>46132</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7442,7 +7452,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7485,7 +7495,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7499,10 +7509,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45723</v>
+        <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7515,7 +7525,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7558,7 +7568,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7572,10 +7582,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45170</v>
+        <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7588,7 +7598,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7631,7 +7641,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7641,14 +7651,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45726</v>
+        <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7661,7 +7671,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7704,7 +7714,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7714,14 +7724,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45441</v>
+        <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7734,7 +7744,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7777,7 +7787,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7791,10 +7801,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45392</v>
+        <v>44700</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7807,7 +7817,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7850,7 +7860,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7864,10 +7874,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45216</v>
+        <v>45329</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7880,7 +7890,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7923,7 +7933,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7933,14 +7943,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44959</v>
+        <v>44746</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7953,7 +7963,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7996,7 +8006,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8010,10 +8020,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45817</v>
+        <v>45723</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8026,7 +8036,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8069,7 +8079,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8083,10 +8093,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45565</v>
+        <v>44712</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8098,13 +8108,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>23.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8147,7 +8152,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8161,10 +8166,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45476</v>
+        <v>45917</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8177,7 +8182,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8220,7 +8225,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8234,10 +8239,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45476</v>
+        <v>45834</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8250,7 +8255,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8293,7 +8298,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8307,10 +8312,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45350</v>
+        <v>46034</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8323,7 +8328,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8366,7 +8371,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8380,10 +8385,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45028</v>
+        <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8395,13 +8400,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8444,7 +8444,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8458,10 +8458,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46206</v>
+        <v>45817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8517,7 +8517,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8527,14 +8527,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45300</v>
+        <v>45589</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8600,14 +8600,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44746</v>
+        <v>44959</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8673,14 +8673,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44710</v>
+        <v>45726</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.9</v>
+        <v>0.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46276</v>
+        <v>45216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>11.6</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46245</v>
+        <v>45817</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45805</v>
+        <v>46206</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8955,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8969,10 +8969,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46290</v>
+        <v>46276</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7.3</v>
+        <v>11.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9038,14 +9038,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45812</v>
+        <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45835</v>
+        <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>44746</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44943</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45968</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44750</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44566</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44532</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44712</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44809</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45350</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45412</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44746</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45170</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44828</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45392</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45345</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45300</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45887</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45350</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45897</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45929</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45145</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>44895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44517</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44943</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45805</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>45055</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45812</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45565</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>45028</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45835</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45971</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44710</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45982</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44704</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45441</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>46132</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44700</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45329</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44746</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45723</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44712</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>45917</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45834</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>46034</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45589</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44959</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45726</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45817</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>46206</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>46276</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>44746</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44943</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44712</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45968</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44750</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44566</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44532</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44712</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44809</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45350</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45412</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44746</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45170</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44828</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45392</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45345</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45300</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45887</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45350</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45897</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45922</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45929</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45145</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>44895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44517</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44517</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44943</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45805</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>45055</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45812</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45565</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>45028</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45835</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45971</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44710</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45982</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44704</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45441</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>46132</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44700</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45329</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44746</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45723</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44712</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>45917</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45834</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>46034</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45589</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44959</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45726</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45817</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>46206</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>46276</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3543-2024</t>
+          <t>A 28233-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45320</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,8 +836,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -846,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -864,18 +869,234 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Björksplintborre
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2443-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Större brunfladdermus
+Vanlig padda
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 3543-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Dolkstekelsglasvinge
@@ -883,264 +1104,43 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28233-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Björksplintborre
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2443-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Större brunfladdermus
-Vanlig padda
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 22268-2022</t>
+          <t>A 55111-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44712</v>
+        <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>16.6</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1206,148 +1206,148 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Stor revmossa
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 22268-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Havstulpanlav
 Stubbspretmossa
 Mattlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 22268-2022 artfynd.xlsx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 22268-2022 karta.png", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 22268-2022 georefererad karta.tif", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 22268-2022 FSC-klagomål.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 22268-2022 FSC-klagomål mail.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 22268-2022 tillsynsbegäran.docx", "A 22268-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 22268-2022 tillsynsbegäran mail.docx", "A 22268-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 55111-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Stor revmossa
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 55111-2025 artfynd.xlsx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 55111-2025 karta.png", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 55111-2025 georefererad karta.tif", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 55111-2025 FSC-klagomål.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 55111-2025 FSC-klagomål mail.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 55111-2025 tillsynsbegäran.docx", "A 55111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 55111-2025 tillsynsbegäran mail.docx", "A 55111-2025")</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44623</v>
+        <v>45282</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2167,42 +2167,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,10 +2220,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45092</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,13 +2236,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2268,39 +2272,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
@@ -2324,7 +2328,7 @@
         <v>45057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2416,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,10 +2430,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45282</v>
+        <v>45092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2442,13 +2446,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2478,43 +2482,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44700</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 29101-2022</t>
+          <t>A 468-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3042,14 +3042,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44750</v>
+        <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 468-2022</t>
+          <t>A 22240-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3115,14 +3115,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44566</v>
+        <v>44712</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 69614-2021</t>
+          <t>A 15138-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44532</v>
+        <v>44658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 69628-2021</t>
+          <t>A 29101-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44532</v>
+        <v>44750</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22240-2022</t>
+          <t>A 69614-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44712</v>
+        <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15138-2022</t>
+          <t>A 69628-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44658</v>
+        <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37441-2022</t>
+          <t>A 38743-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44809</v>
+        <v>45887</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7989-2024</t>
+          <t>A 40848-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45350</v>
+        <v>45897</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50405-2023</t>
+          <t>A 38739-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45216</v>
+        <v>45887</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50410-2023</t>
+          <t>A 790-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45216</v>
+        <v>45300</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17071-2024</t>
+          <t>A 45132-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3772,14 +3772,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45412</v>
+        <v>45919</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28103-2022</t>
+          <t>A 45396-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44746</v>
+        <v>45922</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 40709-2023</t>
+          <t>A 45363-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45170</v>
+        <v>45922</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41836-2022</t>
+          <t>A 45483-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44828</v>
+        <v>45922</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14067-2024</t>
+          <t>A 46957-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45392</v>
+        <v>45929</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7429-2024</t>
+          <t>A 47599-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4137,14 +4137,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45345</v>
+        <v>45931</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50622-2023</t>
+          <t>A 66104-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45217</v>
+        <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 790-2024</t>
+          <t>A 57186-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45300</v>
+        <v>44895</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47866-2024</t>
+          <t>A 57083-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45588</v>
+        <v>44895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47398-2024</t>
+          <t>A 57120-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45587</v>
+        <v>44895</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38739-2025</t>
+          <t>A 36756-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45887</v>
+        <v>44805</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38743-2025</t>
+          <t>A 2450-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45887</v>
+        <v>44943</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7990-2024</t>
+          <t>A 66107-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45350</v>
+        <v>44517</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40848-2025</t>
+          <t>A 66008-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4721,14 +4721,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45897</v>
+        <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28118-2024</t>
+          <t>A 57178-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45476</v>
+        <v>44895</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28139-2024</t>
+          <t>A 57195-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45476</v>
+        <v>44895</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45396-2025</t>
+          <t>A 28157-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>44746</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45483-2025</t>
+          <t>A 7272-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45922</v>
+        <v>44970</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45132-2025</t>
+          <t>A 21836-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5086,14 +5086,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45919</v>
+        <v>44710</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>5.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45363-2025</t>
+          <t>A 50622-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45922</v>
+        <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39113-2024</t>
+          <t>A 55429-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45548</v>
+        <v>45971</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46957-2025</t>
+          <t>A 30034-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45929</v>
+        <v>46206</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.699999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35199-2023</t>
+          <t>A 58042-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5378,14 +5378,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45145</v>
+        <v>45982</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47599-2025</t>
+          <t>A 39113-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45931</v>
+        <v>45548</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5514,7 +5514,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57178-2022</t>
+          <t>A 26073-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44895</v>
+        <v>45805</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66008-2021</t>
+          <t>A 61762-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44517</v>
+        <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 66104-2021</t>
+          <t>A 61766-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44517</v>
+        <v>46002</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66107-2021</t>
+          <t>A 27367-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44517</v>
+        <v>45812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36756-2022</t>
+          <t>A 62769-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44805</v>
+        <v>46008</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57186-2022</t>
+          <t>A 62774-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44895</v>
+        <v>46008</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7272-2023</t>
+          <t>A 37639-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44970</v>
+        <v>46276</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>11.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2450-2023</t>
+          <t>A 4883-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44943</v>
+        <v>45329</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>6.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57083-2022</t>
+          <t>A 32093-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44895</v>
+        <v>45835</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57120-2022</t>
+          <t>A 32095-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44895</v>
+        <v>45835</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57195-2022</t>
+          <t>A 2420-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44895</v>
+        <v>46034</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26073-2025</t>
+          <t>A 2335-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45805</v>
+        <v>46036</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20210-2023</t>
+          <t>A 11232-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6400,14 +6400,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45055</v>
+        <v>45726</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 27367-2025</t>
+          <t>A 33070-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6473,14 +6473,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45812</v>
+        <v>46245</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42526-2024</t>
+          <t>A 47866-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45565</v>
+        <v>45588</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6565,13 +6565,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50397-2023</t>
+          <t>A 39853-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>46290</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6644,7 +6639,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6687,7 +6682,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16648-2023</t>
+          <t>A 13156-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6697,14 +6692,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45028</v>
+        <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6716,13 +6711,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6765,7 +6755,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32095-2025</t>
+          <t>A 35199-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6775,14 +6765,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45835</v>
+        <v>45145</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6795,7 +6785,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6838,7 +6828,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32093-2025</t>
+          <t>A 21133-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6848,14 +6838,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45835</v>
+        <v>44704</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6868,7 +6858,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6911,7 +6901,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13156-2024</t>
+          <t>A 19238-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6921,14 +6911,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45386</v>
+        <v>46132</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6941,7 +6931,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6984,7 +6974,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55429-2025</t>
+          <t>A 20210-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6998,10 +6988,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45971</v>
+        <v>45055</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7014,7 +7004,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7057,7 +7047,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21836-2022</t>
+          <t>A 22300-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7071,10 +7061,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44710</v>
+        <v>44712</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7087,7 +7077,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.9</v>
+        <v>23.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7130,7 +7120,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28089-2022</t>
+          <t>A 44780-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7144,10 +7134,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44746</v>
+        <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7160,7 +7150,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7203,7 +7193,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58042-2025</t>
+          <t>A 28029-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7217,10 +7207,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45982</v>
+        <v>45817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7233,7 +7223,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7276,7 +7266,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21133-2022</t>
+          <t>A 31687-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7286,14 +7276,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44704</v>
+        <v>45834</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7306,7 +7296,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7349,7 +7339,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 24163-2024</t>
+          <t>A 28089-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7359,14 +7349,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45441</v>
+        <v>44746</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7379,7 +7369,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7422,7 +7412,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19238-2026</t>
+          <t>A 47944-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7436,10 +7426,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46132</v>
+        <v>45589</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7452,7 +7442,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7495,7 +7485,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61766-2025</t>
+          <t>A 11124-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7509,10 +7499,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46002</v>
+        <v>45723</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7525,7 +7515,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7568,7 +7558,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61762-2025</t>
+          <t>A 37441-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7582,10 +7572,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46002</v>
+        <v>44809</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7598,7 +7588,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7641,7 +7631,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62769-2025</t>
+          <t>A 50397-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7655,10 +7645,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7671,7 +7661,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7714,7 +7704,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62774-2025</t>
+          <t>A 50420-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7728,10 +7718,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46008</v>
+        <v>45216</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7744,7 +7734,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7787,7 +7777,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20680-2022</t>
+          <t>A 28103-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7801,10 +7791,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44700</v>
+        <v>44746</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7817,7 +7807,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7860,7 +7850,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4883-2024</t>
+          <t>A 7989-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7874,10 +7864,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45329</v>
+        <v>45350</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7890,7 +7880,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7933,7 +7923,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28157-2022</t>
+          <t>A 28053-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7947,10 +7937,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44746</v>
+        <v>45817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7963,7 +7953,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8006,7 +7996,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11124-2025</t>
+          <t>A 50405-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8020,10 +8010,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45723</v>
+        <v>45216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8036,7 +8026,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8079,7 +8069,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22300-2022</t>
+          <t>A 50410-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8093,10 +8083,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44712</v>
+        <v>45216</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8109,7 +8099,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>23.3</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8152,7 +8142,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 44780-2025</t>
+          <t>A 41836-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8166,10 +8156,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45917</v>
+        <v>44828</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8182,7 +8172,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8225,7 +8215,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 31687-2025</t>
+          <t>A 47398-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8239,10 +8229,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45834</v>
+        <v>45587</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8255,7 +8245,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8298,7 +8288,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2420-2026</t>
+          <t>A 7429-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8308,14 +8298,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46034</v>
+        <v>45345</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8328,7 +8318,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8371,7 +8361,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 2335-2026</t>
+          <t>A 17071-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8385,10 +8375,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46036</v>
+        <v>45412</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8401,7 +8391,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8444,7 +8434,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28029-2025</t>
+          <t>A 20680-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8458,10 +8448,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45817</v>
+        <v>44700</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8474,7 +8464,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8517,7 +8507,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47944-2024</t>
+          <t>A 40709-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8531,10 +8521,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45589</v>
+        <v>45170</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8547,7 +8537,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8590,7 +8580,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 5359-2023</t>
+          <t>A 24163-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8604,10 +8594,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44959</v>
+        <v>45441</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8620,7 +8610,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8663,7 +8653,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11232-2025</t>
+          <t>A 14067-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8673,14 +8663,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45726</v>
+        <v>45392</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8693,7 +8683,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8736,7 +8726,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50420-2023</t>
+          <t>A 5359-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8746,14 +8736,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45216</v>
+        <v>44959</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8766,7 +8756,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8809,7 +8799,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28053-2025</t>
+          <t>A 42526-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8823,10 +8813,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45817</v>
+        <v>45565</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8838,8 +8828,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8882,7 +8877,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30034-2026</t>
+          <t>A 28118-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8896,10 +8891,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46206</v>
+        <v>45476</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8912,7 +8907,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8955,7 +8950,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37639-2026</t>
+          <t>A 28139-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8969,10 +8964,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46276</v>
+        <v>45476</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8985,7 +8980,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11.6</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9028,7 +9023,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33070-2026</t>
+          <t>A 7990-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9042,10 +9037,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46245</v>
+        <v>45350</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9058,7 +9053,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9101,7 +9096,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39853-2026</t>
+          <t>A 16648-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9115,10 +9110,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46290</v>
+        <v>45028</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9130,8 +9125,13 @@
           <t>LERUM</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>

--- a/Översikt LERUM.xlsx
+++ b/Översikt LERUM.xlsx
@@ -601,7 +601,7 @@
         <v>44943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28233-2022</t>
+          <t>A 3543-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -836,13 +836,8 @@
           <t>LERUM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -851,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -869,18 +864,135 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönhjon
+Dolkstekelsglasvinge
+Spillkråka
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28233-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Björksplintborre
@@ -888,107 +1000,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 28233-2022 artfynd.xlsx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 28233-2022 karta.png", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 28233-2022 georefererad karta.tif", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 28233-2022 FSC-klagomål.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 28233-2022 FSC-klagomål mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 28233-2022 tillsynsbegäran.docx", "A 28233-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 28233-2022 tillsynsbegäran mail.docx", "A 28233-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2443-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LERUM</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Större brunfladdermus
@@ -996,144 +1108,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 2443-2023 artfynd.xlsx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 2443-2023 karta.png", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 2443-2023 georefererad karta.tif", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 2443-2023 FSC-klagomål.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 2443-2023 FSC-klagomål mail.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 2443-2023 tillsynsbegäran.docx", "A 2443-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 2443-2023 tillsynsbegäran mail.docx", "A 2443-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 3543-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LERUM</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönhjon
-Dolkstekelsglasvinge
-Spillkråka
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 3543-2024 artfynd.xlsx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 3543-2024 karta.png", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 3543-2024 georefererad karta.tif", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 3543-2024 FSC-klagomål.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 3543-2024 FSC-klagomål mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 3543-2024 tillsynsbegäran.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 3543-2024 tillsynsbegäran mail.docx", "A 3543-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 3543-2024 prioriterade fågelarter.docx", "A 3543-2024")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>45968</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44735</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>44943</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>44895</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44943</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 64855-2023</t>
+          <t>A 26568-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45282</v>
+        <v>45092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2163,50 +2163,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx", "A 64855-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/fåglar/A 64855-2023 prioriterade fågelarter.docx", "A 64855-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10410-2022</t>
+          <t>A 20570-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2220,10 +2216,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44623</v>
+        <v>45057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2236,13 +2232,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2272,46 +2268,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20570-2023</t>
+          <t>A 10410-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2325,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45057</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2341,13 +2337,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2377,46 +2373,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 20570-2023 artfynd.xlsx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 10410-2022 artfynd.xlsx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 20570-2023 karta.png", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 10410-2022 karta.png", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 20570-2023 georefererad karta.tif", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 10410-2022 georefererad karta.tif", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 20570-2023 FSC-klagomål.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 10410-2022 FSC-klagomål.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 20570-2023 FSC-klagomål mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 10410-2022 FSC-klagomål mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 20570-2023 tillsynsbegäran.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 10410-2022 tillsynsbegäran.docx", "A 10410-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 20570-2023 tillsynsbegäran mail.docx", "A 20570-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 10410-2022 tillsynsbegäran mail.docx", "A 10410-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26568-2023</t>
+          <t>A 64855-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2430,10 +2426,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45092</v>
+        <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2446,13 +2442,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2482,39 +2478,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 26568-2023 artfynd.xlsx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/artfynd/A 64855-2023 artfynd.xlsx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 26568-2023 karta.png", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor/A 64855-2023 karta.png", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 26568-2023 georefererad karta.tif", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/kartor_geotiff/A 64855-2023 georefererad karta.tif", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 26568-2023 FSC-klagomål.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomål/A 64855-2023 FSC-klagomål.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 26568-2023 FSC-klagomål mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/klagomålsmail/A 64855-2023 FSC-klagomål mail.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 26568-2023 tillsynsbegäran.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsyn/A 64855-2023 tillsynsbegäran.docx", "A 64855-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 26568-2023 tillsynsbegäran mail.docx", "A 26568-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1441/tillsynsmail/A 64855-2023 tillsynsbegäran mail.docx